--- a/task193/golden/sequence_screen_2027Q1.xlsx
+++ b/task193/golden/sequence_screen_2027Q1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="95">
   <si>
     <t>Prescription-sequence screen, run of October 2026</t>
   </si>
@@ -162,7 +162,7 @@
     <t>Dispensing lines by chain and quarter of dispensing</t>
   </si>
   <si>
-    <t>Accepted lines are the rows in the two register extracts; lines turned back at validation are in submission_exceptions.csv and never reach them.</t>
+    <t>Quarters are quarters of dispensing. Accepted lines are the distinct dispensings in the two register extracts, counting a re-sent line once; lines turned back at validation are in submission_exceptions.csv and never reach the extracts.</t>
   </si>
   <si>
     <t>Chain</t>
@@ -207,7 +207,7 @@
     <t>Statutory data fee, screen window 2025-26</t>
   </si>
   <si>
-    <t>Doses at the rates in schedule 3, with the amendment of 1 April 2026 applied to doses dispensed on or after that date. Strandby Farma's doses are charged to Bregnholt from the merger on 1 April 2026.</t>
+    <t>Doses at the rates in schedule 3, with the amendment of 1 April 2026 applied to doses dispensed on or after that date, and each payer's band rate charged on all of its doses. Sovraxil's doses move to Ellevang with the authorisation on 27 February 2026; Strandby's own doses before the merger of 1 April 2026 are charged to Strandby and its later doses to Bregnholt. Re-sent lines are counted once.</t>
   </si>
   <si>
     <t>Holder</t>
@@ -256,6 +256,12 @@
   </si>
   <si>
     <t>Ellevang Biosciences A/S</t>
+  </si>
+  <si>
+    <t>H7</t>
+  </si>
+  <si>
+    <t>Strandby Farma ApS</t>
   </si>
   <si>
     <t>Patients with a first receipt of a screened product in the window</t>
@@ -1535,10 +1541,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>5795</v>
+        <v>4500</v>
       </c>
       <c r="D5">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E5" s="5">
         <v>2</v>
@@ -1552,13 +1558,13 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>4044</v>
+        <v>4156</v>
       </c>
       <c r="D6">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="E6" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1569,13 +1575,13 @@
         <v>55</v>
       </c>
       <c r="C7">
-        <v>3995</v>
+        <v>4068</v>
       </c>
       <c r="D7">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="E7" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1586,13 +1592,13 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>4379</v>
+        <v>4374</v>
       </c>
       <c r="D8">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="E8" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1603,10 +1609,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>3455</v>
+        <v>3448</v>
       </c>
       <c r="D9">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E9" s="5">
         <v>4</v>
@@ -1620,10 +1626,10 @@
         <v>54</v>
       </c>
       <c r="C10">
-        <v>3077</v>
+        <v>3067</v>
       </c>
       <c r="D10">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="E10" s="5">
         <v>4</v>
@@ -1637,13 +1643,13 @@
         <v>55</v>
       </c>
       <c r="C11">
-        <v>2993</v>
+        <v>2909</v>
       </c>
       <c r="D11">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E11" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1654,13 +1660,13 @@
         <v>56</v>
       </c>
       <c r="C12">
-        <v>3213</v>
+        <v>3216</v>
       </c>
       <c r="D12">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E12" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1671,10 +1677,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>2451</v>
+        <v>2432</v>
       </c>
       <c r="D13">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E13" s="5">
         <v>5</v>
@@ -1688,13 +1694,13 @@
         <v>54</v>
       </c>
       <c r="C14">
-        <v>2291</v>
+        <v>2306</v>
       </c>
       <c r="D14">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E14" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1705,13 +1711,13 @@
         <v>55</v>
       </c>
       <c r="C15">
-        <v>2288</v>
+        <v>2250</v>
       </c>
       <c r="D15">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E15" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1722,10 +1728,10 @@
         <v>56</v>
       </c>
       <c r="C16">
-        <v>2323</v>
+        <v>2351</v>
       </c>
       <c r="D16">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E16" s="5">
         <v>6</v>
@@ -1739,10 +1745,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1714</v>
+        <v>1706</v>
       </c>
       <c r="D17">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E17" s="5">
         <v>7</v>
@@ -1756,13 +1762,13 @@
         <v>54</v>
       </c>
       <c r="C18">
-        <v>1540</v>
+        <v>1555</v>
       </c>
       <c r="D18">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E18" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1773,10 +1779,10 @@
         <v>55</v>
       </c>
       <c r="C19">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="D19">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E19" s="5">
         <v>7</v>
@@ -1790,13 +1796,13 @@
         <v>56</v>
       </c>
       <c r="C20">
-        <v>1696</v>
+        <v>1701</v>
       </c>
       <c r="D20">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E20" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1806,7 +1812,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6B631E-BAF0-5A40-8D83-136CD67900E4}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -1847,10 +1853,10 @@
         <v>67</v>
       </c>
       <c r="C5" s="10">
-        <v>195245.6</v>
+        <v>101540.2</v>
       </c>
       <c r="D5" s="11">
-        <v>304488</v>
+        <v>156088</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1861,10 +1867,10 @@
         <v>69</v>
       </c>
       <c r="C6" s="10">
-        <v>108844.8</v>
+        <v>92050.3</v>
       </c>
       <c r="D6" s="11">
-        <v>168802</v>
+        <v>144276</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1875,10 +1881,10 @@
         <v>71</v>
       </c>
       <c r="C7" s="10">
-        <v>97738.8</v>
+        <v>333552</v>
       </c>
       <c r="D7" s="11">
-        <v>155320</v>
+        <v>443762</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1889,10 +1895,10 @@
         <v>73</v>
       </c>
       <c r="C8" s="10">
-        <v>165851.6</v>
+        <v>149580</v>
       </c>
       <c r="D8" s="11">
-        <v>247642</v>
+        <v>223139</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1903,10 +1909,10 @@
         <v>75</v>
       </c>
       <c r="C9" s="10">
-        <v>133872.2</v>
+        <v>418008</v>
       </c>
       <c r="D9" s="11">
-        <v>202962</v>
+        <v>526452</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1917,10 +1923,24 @@
         <v>77</v>
       </c>
       <c r="C10" s="10">
-        <v>341279.9</v>
+        <v>457387.2</v>
       </c>
       <c r="D10" s="11">
-        <v>441906</v>
+        <v>594129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="10">
+        <v>51710.4</v>
+      </c>
+      <c r="D11" s="11">
+        <v>76531</v>
       </c>
     </row>
   </sheetData>
@@ -1941,34 +1961,34 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5">
         <v>676</v>
@@ -1979,10 +1999,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C6">
         <v>653</v>
@@ -1993,10 +2013,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C7">
         <v>489</v>
@@ -2007,10 +2027,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C8">
         <v>506</v>
@@ -2021,10 +2041,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C9">
         <v>516</v>
@@ -2035,10 +2055,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C10">
         <v>484</v>
@@ -2049,10 +2069,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" t="s">
         <v>88</v>
-      </c>
-      <c r="B11" t="s">
-        <v>86</v>
       </c>
       <c r="C11">
         <v>331</v>
@@ -2063,10 +2083,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C12">
         <v>388</v>
@@ -2077,10 +2097,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C13">
         <v>245</v>
@@ -2091,10 +2111,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C14">
         <v>176</v>
@@ -2105,10 +2125,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C15">
         <v>164</v>
@@ -2119,10 +2139,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" t="s">
         <v>89</v>
-      </c>
-      <c r="B16" t="s">
-        <v>87</v>
       </c>
       <c r="C16">
         <v>168</v>
@@ -2133,10 +2153,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C17">
         <v>320</v>
@@ -2147,10 +2167,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C18">
         <v>274</v>
@@ -2161,10 +2181,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C19">
         <v>242</v>
@@ -2175,10 +2195,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C20">
         <v>221</v>
@@ -2189,10 +2209,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C21">
         <v>445</v>
@@ -2203,10 +2223,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C22">
         <v>414</v>
@@ -2217,10 +2237,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C23">
         <v>332</v>
@@ -2231,10 +2251,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C24">
         <v>363</v>
@@ -2245,10 +2265,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C25">
         <v>48</v>
@@ -2259,10 +2279,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C26">
         <v>63</v>
@@ -2273,10 +2293,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C27">
         <v>35</v>
@@ -2287,10 +2307,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C28">
         <v>41</v>

--- a/task193/golden/sequence_screen_2027Q1.xlsx
+++ b/task193/golden/sequence_screen_2027Q1.xlsx
@@ -156,7 +156,7 @@
     <t>Pairs below the 25-patient minimum are shown with no figures and are carried forward to the next run under section 3.4.</t>
   </si>
   <si>
-    <t>Nearest pair on the wrong side of the line: Dalvextin and acid-suppressant, multiple 1.12.</t>
+    <t>Nearest pair on the wrong side of the line: Dalvextin and acid-suppressant, multiple 1.13.</t>
   </si>
   <si>
     <t>Dispensing lines by chain and quarter of dispensing</t>
@@ -773,22 +773,22 @@
         <v>15</v>
       </c>
       <c r="D6">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="E6">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F6">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G6" s="4">
-        <v>0.5329999999999999</v>
+        <v>0.547</v>
       </c>
       <c r="H6" s="5">
-        <v>72.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I6" s="6">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="J6" t="s">
         <v>16</v>
@@ -808,19 +808,19 @@
         <v>135</v>
       </c>
       <c r="E7">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G7" s="4">
-        <v>0.5479999999999999</v>
+        <v>0.541</v>
       </c>
       <c r="H7" s="5">
-        <v>75.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I7" s="6">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
@@ -837,22 +837,22 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="E8">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="F8">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G8" s="4">
-        <v>0.774</v>
+        <v>0.75</v>
       </c>
       <c r="H8" s="5">
-        <v>139.6</v>
+        <v>133</v>
       </c>
       <c r="I8" s="6">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -869,22 +869,22 @@
         <v>15</v>
       </c>
       <c r="D9">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="E9">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="F9">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G9" s="4">
-        <v>0.7390000000000001</v>
+        <v>0.723</v>
       </c>
       <c r="H9" s="5">
-        <v>150.2</v>
+        <v>138.1</v>
       </c>
       <c r="I9" s="6">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -901,22 +901,22 @@
         <v>22</v>
       </c>
       <c r="D10">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E10">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F10">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G10" s="4">
-        <v>0.555</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H10" s="5">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I10" s="6">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="s">
         <v>16</v>
@@ -936,19 +936,19 @@
         <v>134</v>
       </c>
       <c r="E11">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G11" s="4">
-        <v>0.545</v>
+        <v>0.552</v>
       </c>
       <c r="H11" s="5">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I11" s="6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="J11" t="s">
         <v>16</v>
@@ -965,22 +965,22 @@
         <v>26</v>
       </c>
       <c r="D12">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="E12">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F12">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="G12" s="4">
-        <v>0.238</v>
+        <v>0.241</v>
       </c>
       <c r="H12" s="5">
-        <v>61.7</v>
+        <v>60.2</v>
       </c>
       <c r="I12" s="6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="J12" t="s">
         <v>16</v>
@@ -997,19 +997,19 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="E13">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="F13">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G13" s="4">
-        <v>0.511</v>
+        <v>0.508</v>
       </c>
       <c r="H13" s="5">
-        <v>146.4</v>
+        <v>137.7</v>
       </c>
       <c r="I13" s="6">
         <v>1.39</v>
@@ -1029,22 +1029,22 @@
         <v>23</v>
       </c>
       <c r="D14">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="E14">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F14">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="G14" s="4">
-        <v>0.204</v>
+        <v>0.211</v>
       </c>
       <c r="H14" s="5">
-        <v>59.6</v>
+        <v>54.1</v>
       </c>
       <c r="I14" s="6">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="J14" t="s">
         <v>16</v>
@@ -1061,22 +1061,22 @@
         <v>18</v>
       </c>
       <c r="D15">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="E15">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="F15">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="G15" s="4">
-        <v>0.307</v>
+        <v>0.292</v>
       </c>
       <c r="H15" s="5">
-        <v>107</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I15" s="6">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="J15" t="s">
         <v>16</v>
@@ -1093,22 +1093,22 @@
         <v>22</v>
       </c>
       <c r="D16">
-        <v>551</v>
+        <v>523</v>
       </c>
       <c r="E16">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="F16">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="G16" s="4">
-        <v>0.5639999999999999</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="H16" s="5">
-        <v>232.9</v>
+        <v>225.5</v>
       </c>
       <c r="I16" s="6">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
@@ -1125,22 +1125,22 @@
         <v>29</v>
       </c>
       <c r="D17">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="E17">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F17">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="G17" s="4">
-        <v>0.358</v>
+        <v>0.351</v>
       </c>
       <c r="H17" s="5">
-        <v>125.6</v>
+        <v>118.3</v>
       </c>
       <c r="I17" s="6">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="J17" t="s">
         <v>16</v>
@@ -1157,22 +1157,22 @@
         <v>26</v>
       </c>
       <c r="D18">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="E18">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F18">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G18" s="4">
-        <v>0.779</v>
+        <v>0.792</v>
       </c>
       <c r="H18" s="5">
-        <v>186.2</v>
+        <v>175.2</v>
       </c>
       <c r="I18" s="6">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="J18" t="s">
         <v>16</v>
@@ -1189,22 +1189,22 @@
         <v>15</v>
       </c>
       <c r="D19">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="E19">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="F19">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G19" s="4">
-        <v>0.8029999999999999</v>
+        <v>0.8079999999999999</v>
       </c>
       <c r="H19" s="5">
-        <v>210.8</v>
+        <v>197.8</v>
       </c>
       <c r="I19" s="6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="J19" t="s">
         <v>16</v>
@@ -1221,10 +1221,10 @@
         <v>23</v>
       </c>
       <c r="D20">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E20">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F20">
         <v>32</v>
@@ -1233,10 +1233,10 @@
         <v>0.8640000000000001</v>
       </c>
       <c r="H20" s="5">
-        <v>200</v>
+        <v>200.8</v>
       </c>
       <c r="I20" s="6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="J20" t="s">
         <v>16</v>
@@ -1253,19 +1253,19 @@
         <v>26</v>
       </c>
       <c r="D21">
-        <v>354</v>
+        <v>329</v>
       </c>
       <c r="E21">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="F21">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G21" s="4">
-        <v>0.701</v>
+        <v>0.7020000000000001</v>
       </c>
       <c r="H21" s="5">
-        <v>168.8</v>
+        <v>157.7</v>
       </c>
       <c r="I21" s="6">
         <v>1.47</v>
@@ -1285,13 +1285,13 @@
         <v>34</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J22" t="s">
         <v>35</v>
@@ -1308,22 +1308,22 @@
         <v>23</v>
       </c>
       <c r="D23">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="E23">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="F23">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G23" s="4">
-        <v>0.723</v>
+        <v>0.716</v>
       </c>
       <c r="H23" s="5">
-        <v>130.9</v>
+        <v>121.1</v>
       </c>
       <c r="I23" s="6">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
@@ -1363,22 +1363,22 @@
         <v>18</v>
       </c>
       <c r="D25">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E25">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F25">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G25" s="4">
-        <v>0.767</v>
+        <v>0.7609999999999999</v>
       </c>
       <c r="H25" s="5">
-        <v>153.3</v>
+        <v>153.6</v>
       </c>
       <c r="I25" s="6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="J25" t="s">
         <v>16</v>
@@ -1395,22 +1395,22 @@
         <v>22</v>
       </c>
       <c r="D26">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E26">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F26">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G26" s="4">
-        <v>0.763</v>
+        <v>0.78</v>
       </c>
       <c r="H26" s="5">
-        <v>165</v>
+        <v>165.7</v>
       </c>
       <c r="I26" s="6">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="J26" t="s">
         <v>16</v>
@@ -1427,22 +1427,22 @@
         <v>29</v>
       </c>
       <c r="D27">
-        <v>469</v>
+        <v>432</v>
       </c>
       <c r="E27">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="F27">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="G27" s="4">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="H27" s="5">
-        <v>257.4</v>
+        <v>238.2</v>
       </c>
       <c r="I27" s="6">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
@@ -1459,10 +1459,10 @@
         <v>34</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28">
         <v>4</v>
@@ -1541,13 +1541,13 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>4500</v>
+        <v>4588</v>
       </c>
       <c r="D5">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="E5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1558,13 +1558,13 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>4156</v>
+        <v>4101</v>
       </c>
       <c r="D6">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E6" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1575,13 +1575,13 @@
         <v>55</v>
       </c>
       <c r="C7">
-        <v>4068</v>
+        <v>3966</v>
       </c>
       <c r="D7">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E7" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1592,13 +1592,13 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>4374</v>
+        <v>4303</v>
       </c>
       <c r="D8">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="E8" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1609,13 +1609,13 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>3448</v>
+        <v>3548</v>
       </c>
       <c r="D9">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="E9" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1629,10 +1629,10 @@
         <v>3067</v>
       </c>
       <c r="D10">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E10" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1643,13 +1643,13 @@
         <v>55</v>
       </c>
       <c r="C11">
-        <v>2909</v>
+        <v>3016</v>
       </c>
       <c r="D11">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="E11" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1660,13 +1660,13 @@
         <v>56</v>
       </c>
       <c r="C12">
-        <v>3216</v>
+        <v>3190</v>
       </c>
       <c r="D12">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E12" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1677,13 +1677,13 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>2432</v>
+        <v>2441</v>
       </c>
       <c r="D13">
         <v>74</v>
       </c>
       <c r="E13" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1694,13 +1694,13 @@
         <v>54</v>
       </c>
       <c r="C14">
-        <v>2306</v>
+        <v>2300</v>
       </c>
       <c r="D14">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E14" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1711,13 +1711,13 @@
         <v>55</v>
       </c>
       <c r="C15">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="D15">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E15" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1728,13 +1728,13 @@
         <v>56</v>
       </c>
       <c r="C16">
-        <v>2351</v>
+        <v>2326</v>
       </c>
       <c r="D16">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E16" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1745,13 +1745,13 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1706</v>
+        <v>1678</v>
       </c>
       <c r="D17">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E17" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1762,13 +1762,13 @@
         <v>54</v>
       </c>
       <c r="C18">
-        <v>1555</v>
+        <v>1541</v>
       </c>
       <c r="D18">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="E18" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1779,13 +1779,13 @@
         <v>55</v>
       </c>
       <c r="C19">
-        <v>1496</v>
+        <v>1483</v>
       </c>
       <c r="D19">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E19" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1796,13 +1796,13 @@
         <v>56</v>
       </c>
       <c r="C20">
-        <v>1701</v>
+        <v>1666</v>
       </c>
       <c r="D20">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E20" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1853,10 +1853,10 @@
         <v>67</v>
       </c>
       <c r="C5" s="10">
-        <v>101540.2</v>
+        <v>184847.5</v>
       </c>
       <c r="D5" s="11">
-        <v>156088</v>
+        <v>284155</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1867,10 +1867,10 @@
         <v>69</v>
       </c>
       <c r="C6" s="10">
-        <v>92050.3</v>
+        <v>176719.6</v>
       </c>
       <c r="D6" s="11">
-        <v>144276</v>
+        <v>275837</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1881,10 +1881,10 @@
         <v>71</v>
       </c>
       <c r="C7" s="10">
-        <v>333552</v>
+        <v>309372</v>
       </c>
       <c r="D7" s="11">
-        <v>443762</v>
+        <v>411485</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1895,10 +1895,10 @@
         <v>73</v>
       </c>
       <c r="C8" s="10">
-        <v>149580</v>
+        <v>124630.3</v>
       </c>
       <c r="D8" s="11">
-        <v>223139</v>
+        <v>184942</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1909,10 +1909,10 @@
         <v>75</v>
       </c>
       <c r="C9" s="10">
-        <v>418008</v>
+        <v>101506.8</v>
       </c>
       <c r="D9" s="11">
-        <v>526452</v>
+        <v>151463</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1923,10 +1923,10 @@
         <v>77</v>
       </c>
       <c r="C10" s="10">
-        <v>457387.2</v>
+        <v>283991</v>
       </c>
       <c r="D10" s="11">
-        <v>594129</v>
+        <v>362901</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1937,10 +1937,10 @@
         <v>79</v>
       </c>
       <c r="C11" s="10">
-        <v>51710.4</v>
+        <v>75789</v>
       </c>
       <c r="D11" s="11">
-        <v>76531</v>
+        <v>112168</v>
       </c>
     </row>
   </sheetData>
@@ -1991,10 +1991,10 @@
         <v>86</v>
       </c>
       <c r="C5">
-        <v>676</v>
+        <v>709</v>
       </c>
       <c r="D5" s="4">
-        <v>0.762</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2005,10 +2005,10 @@
         <v>87</v>
       </c>
       <c r="C6">
-        <v>653</v>
+        <v>561</v>
       </c>
       <c r="D6" s="4">
-        <v>0.7490000000000001</v>
+        <v>0.7240000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2019,10 +2019,10 @@
         <v>88</v>
       </c>
       <c r="C7">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="D7" s="4">
-        <v>0.7609999999999999</v>
+        <v>0.789</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2033,10 +2033,10 @@
         <v>89</v>
       </c>
       <c r="C8">
-        <v>506</v>
+        <v>568</v>
       </c>
       <c r="D8" s="4">
-        <v>0.7509999999999999</v>
+        <v>0.8079999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2047,10 +2047,10 @@
         <v>86</v>
       </c>
       <c r="C9">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="D9" s="4">
-        <v>0.7909999999999999</v>
+        <v>0.701</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2061,10 +2061,10 @@
         <v>87</v>
       </c>
       <c r="C10">
-        <v>484</v>
+        <v>456</v>
       </c>
       <c r="D10" s="4">
-        <v>0.789</v>
+        <v>0.741</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2078,7 +2078,7 @@
         <v>331</v>
       </c>
       <c r="D11" s="4">
-        <v>0.7340000000000001</v>
+        <v>0.8009999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2089,10 +2089,10 @@
         <v>89</v>
       </c>
       <c r="C12">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D12" s="4">
-        <v>0.7909999999999999</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2103,10 +2103,10 @@
         <v>86</v>
       </c>
       <c r="C13">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D13" s="4">
-        <v>0.7759999999999999</v>
+        <v>0.6970000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2117,10 +2117,10 @@
         <v>87</v>
       </c>
       <c r="C14">
-        <v>176</v>
+        <v>212</v>
       </c>
       <c r="D14" s="4">
-        <v>0.767</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2131,10 +2131,10 @@
         <v>88</v>
       </c>
       <c r="C15">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="D15" s="4">
-        <v>0.8109999999999999</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2145,10 +2145,10 @@
         <v>89</v>
       </c>
       <c r="C16">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D16" s="4">
-        <v>0.7559999999999999</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2159,10 +2159,10 @@
         <v>86</v>
       </c>
       <c r="C17">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="D17" s="4">
-        <v>0.775</v>
+        <v>0.659</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2173,10 +2173,10 @@
         <v>87</v>
       </c>
       <c r="C18">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D18" s="4">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2187,10 +2187,10 @@
         <v>88</v>
       </c>
       <c r="C19">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="D19" s="4">
-        <v>0.731</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2201,10 +2201,10 @@
         <v>89</v>
       </c>
       <c r="C20">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="D20" s="4">
-        <v>0.76</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2215,10 +2215,10 @@
         <v>86</v>
       </c>
       <c r="C21">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D21" s="4">
-        <v>0.789</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2229,10 +2229,10 @@
         <v>87</v>
       </c>
       <c r="C22">
-        <v>414</v>
+        <v>444</v>
       </c>
       <c r="D22" s="4">
-        <v>0.746</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2243,10 +2243,10 @@
         <v>88</v>
       </c>
       <c r="C23">
-        <v>332</v>
+        <v>282</v>
       </c>
       <c r="D23" s="4">
-        <v>0.75</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2257,10 +2257,10 @@
         <v>89</v>
       </c>
       <c r="C24">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="D24" s="4">
-        <v>0.777</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2271,10 +2271,10 @@
         <v>86</v>
       </c>
       <c r="C25">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D25" s="4">
-        <v>0.7290000000000001</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2285,10 +2285,10 @@
         <v>87</v>
       </c>
       <c r="C26">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D26" s="4">
-        <v>0.873</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2299,10 +2299,10 @@
         <v>88</v>
       </c>
       <c r="C27">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D27" s="4">
-        <v>0.6859999999999999</v>
+        <v>0.7829999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2313,10 +2313,10 @@
         <v>89</v>
       </c>
       <c r="C28">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D28" s="4">
-        <v>0.732</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>

--- a/task193/golden/sequence_screen_2027Q1.xlsx
+++ b/task193/golden/sequence_screen_2027Q1.xlsx
@@ -156,7 +156,7 @@
     <t>Pairs below the 25-patient minimum are shown with no figures and are carried forward to the next run under section 3.4.</t>
   </si>
   <si>
-    <t>Nearest pair on the wrong side of the line: Dalvextin and acid-suppressant, multiple 1.13.</t>
+    <t>Nearest pair on the wrong side of the line: Dalvextin and acid-suppressant, multiple 1.07.</t>
   </si>
   <si>
     <t>Dispensing lines by chain and quarter of dispensing</t>
@@ -773,22 +773,22 @@
         <v>15</v>
       </c>
       <c r="D6">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="E6">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="F6">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="G6" s="4">
-        <v>0.547</v>
+        <v>0.511</v>
       </c>
       <c r="H6" s="5">
-        <v>66.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="I6" s="6">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="J6" t="s">
         <v>16</v>
@@ -805,22 +805,22 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="E7">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="F7">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="G7" s="4">
-        <v>0.541</v>
+        <v>0.5479999999999999</v>
       </c>
       <c r="H7" s="5">
-        <v>74.90000000000001</v>
+        <v>103.6</v>
       </c>
       <c r="I7" s="6">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
@@ -837,22 +837,22 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>244</v>
+        <v>333</v>
       </c>
       <c r="E8">
-        <v>183</v>
+        <v>242</v>
       </c>
       <c r="F8">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="G8" s="4">
-        <v>0.75</v>
+        <v>0.727</v>
       </c>
       <c r="H8" s="5">
-        <v>133</v>
+        <v>170.4</v>
       </c>
       <c r="I8" s="6">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -869,22 +869,22 @@
         <v>15</v>
       </c>
       <c r="D9">
-        <v>271</v>
+        <v>338</v>
       </c>
       <c r="E9">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="F9">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="G9" s="4">
-        <v>0.723</v>
+        <v>0.728</v>
       </c>
       <c r="H9" s="5">
-        <v>138.1</v>
+        <v>175.1</v>
       </c>
       <c r="I9" s="6">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -901,22 +901,22 @@
         <v>22</v>
       </c>
       <c r="D10">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="E10">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F10">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G10" s="4">
-        <v>0.5629999999999999</v>
+        <v>0.551</v>
       </c>
       <c r="H10" s="5">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="I10" s="6">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="J10" t="s">
         <v>16</v>
@@ -933,19 +933,19 @@
         <v>23</v>
       </c>
       <c r="D11">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="E11">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F11">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="G11" s="4">
-        <v>0.552</v>
+        <v>0.539</v>
       </c>
       <c r="H11" s="5">
-        <v>72.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I11" s="6">
         <v>1.02</v>
@@ -965,22 +965,22 @@
         <v>26</v>
       </c>
       <c r="D12">
-        <v>257</v>
+        <v>336</v>
       </c>
       <c r="E12">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F12">
-        <v>195</v>
+        <v>268</v>
       </c>
       <c r="G12" s="4">
-        <v>0.241</v>
+        <v>0.202</v>
       </c>
       <c r="H12" s="5">
-        <v>60.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I12" s="6">
-        <v>1.03</v>
+        <v>0.93</v>
       </c>
       <c r="J12" t="s">
         <v>16</v>
@@ -997,22 +997,22 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>378</v>
+        <v>540</v>
       </c>
       <c r="E13">
-        <v>192</v>
+        <v>275</v>
       </c>
       <c r="F13">
-        <v>186</v>
+        <v>265</v>
       </c>
       <c r="G13" s="4">
-        <v>0.508</v>
+        <v>0.509</v>
       </c>
       <c r="H13" s="5">
-        <v>137.7</v>
+        <v>195.2</v>
       </c>
       <c r="I13" s="6">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -1029,22 +1029,22 @@
         <v>23</v>
       </c>
       <c r="D14">
-        <v>251</v>
+        <v>339</v>
       </c>
       <c r="E14">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F14">
-        <v>198</v>
+        <v>267</v>
       </c>
       <c r="G14" s="4">
-        <v>0.211</v>
+        <v>0.212</v>
       </c>
       <c r="H14" s="5">
-        <v>54.1</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I14" s="6">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="J14" t="s">
         <v>16</v>
@@ -1061,22 +1061,22 @@
         <v>18</v>
       </c>
       <c r="D15">
-        <v>298</v>
+        <v>435</v>
       </c>
       <c r="E15">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="F15">
-        <v>211</v>
+        <v>293</v>
       </c>
       <c r="G15" s="4">
-        <v>0.292</v>
+        <v>0.326</v>
       </c>
       <c r="H15" s="5">
-        <v>97.90000000000001</v>
+        <v>142.6</v>
       </c>
       <c r="I15" s="6">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="J15" t="s">
         <v>16</v>
@@ -1093,22 +1093,22 @@
         <v>22</v>
       </c>
       <c r="D16">
-        <v>523</v>
+        <v>700</v>
       </c>
       <c r="E16">
-        <v>296</v>
+        <v>406</v>
       </c>
       <c r="F16">
-        <v>227</v>
+        <v>294</v>
       </c>
       <c r="G16" s="4">
-        <v>0.5660000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H16" s="5">
-        <v>225.5</v>
+        <v>290.6</v>
       </c>
       <c r="I16" s="6">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
@@ -1125,22 +1125,22 @@
         <v>29</v>
       </c>
       <c r="D17">
-        <v>350</v>
+        <v>494</v>
       </c>
       <c r="E17">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="F17">
-        <v>227</v>
+        <v>356</v>
       </c>
       <c r="G17" s="4">
-        <v>0.351</v>
+        <v>0.279</v>
       </c>
       <c r="H17" s="5">
-        <v>118.3</v>
+        <v>137.6</v>
       </c>
       <c r="I17" s="6">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="J17" t="s">
         <v>16</v>
@@ -1157,22 +1157,22 @@
         <v>26</v>
       </c>
       <c r="D18">
-        <v>226</v>
+        <v>266</v>
       </c>
       <c r="E18">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="F18">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G18" s="4">
-        <v>0.792</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H18" s="5">
-        <v>175.2</v>
+        <v>215.9</v>
       </c>
       <c r="I18" s="6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="J18" t="s">
         <v>16</v>
@@ -1189,19 +1189,19 @@
         <v>15</v>
       </c>
       <c r="D19">
-        <v>245</v>
+        <v>291</v>
       </c>
       <c r="E19">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="F19">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="G19" s="4">
-        <v>0.8079999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="H19" s="5">
-        <v>197.8</v>
+        <v>224.8</v>
       </c>
       <c r="I19" s="6">
         <v>1</v>
@@ -1221,22 +1221,22 @@
         <v>23</v>
       </c>
       <c r="D20">
-        <v>235</v>
+        <v>268</v>
       </c>
       <c r="E20">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F20">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G20" s="4">
-        <v>0.8640000000000001</v>
+        <v>0.784</v>
       </c>
       <c r="H20" s="5">
-        <v>200.8</v>
+        <v>210.1</v>
       </c>
       <c r="I20" s="6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="J20" t="s">
         <v>16</v>
@@ -1253,22 +1253,22 @@
         <v>26</v>
       </c>
       <c r="D21">
-        <v>329</v>
+        <v>434</v>
       </c>
       <c r="E21">
-        <v>231</v>
+        <v>316</v>
       </c>
       <c r="F21">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="G21" s="4">
-        <v>0.7020000000000001</v>
+        <v>0.728</v>
       </c>
       <c r="H21" s="5">
-        <v>157.7</v>
+        <v>215.8</v>
       </c>
       <c r="I21" s="6">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="J21" t="s">
         <v>19</v>
@@ -1285,13 +1285,13 @@
         <v>34</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J22" t="s">
         <v>35</v>
@@ -1308,22 +1308,22 @@
         <v>23</v>
       </c>
       <c r="D23">
-        <v>229</v>
+        <v>276</v>
       </c>
       <c r="E23">
-        <v>164</v>
+        <v>209</v>
       </c>
       <c r="F23">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G23" s="4">
-        <v>0.716</v>
+        <v>0.757</v>
       </c>
       <c r="H23" s="5">
-        <v>121.1</v>
+        <v>148.4</v>
       </c>
       <c r="I23" s="6">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
@@ -1340,13 +1340,13 @@
         <v>34</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J24" t="s">
         <v>35</v>
@@ -1363,19 +1363,19 @@
         <v>18</v>
       </c>
       <c r="D25">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="E25">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="F25">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G25" s="4">
-        <v>0.7609999999999999</v>
+        <v>0.769</v>
       </c>
       <c r="H25" s="5">
-        <v>153.6</v>
+        <v>166.1</v>
       </c>
       <c r="I25" s="6">
         <v>1</v>
@@ -1395,22 +1395,22 @@
         <v>22</v>
       </c>
       <c r="D26">
-        <v>214</v>
+        <v>255</v>
       </c>
       <c r="E26">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="F26">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G26" s="4">
-        <v>0.78</v>
+        <v>0.7879999999999999</v>
       </c>
       <c r="H26" s="5">
-        <v>165.7</v>
+        <v>195.9</v>
       </c>
       <c r="I26" s="6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="J26" t="s">
         <v>16</v>
@@ -1427,22 +1427,22 @@
         <v>29</v>
       </c>
       <c r="D27">
-        <v>432</v>
+        <v>556</v>
       </c>
       <c r="E27">
-        <v>337</v>
+        <v>430</v>
       </c>
       <c r="F27">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="G27" s="4">
-        <v>0.78</v>
+        <v>0.773</v>
       </c>
       <c r="H27" s="5">
-        <v>238.2</v>
+        <v>298.8</v>
       </c>
       <c r="I27" s="6">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
@@ -1459,13 +1459,13 @@
         <v>34</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J28" t="s">
         <v>35</v>
@@ -1541,10 +1541,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>4588</v>
+        <v>5869</v>
       </c>
       <c r="D5">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -1558,10 +1558,10 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>4101</v>
+        <v>5325</v>
       </c>
       <c r="D6">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="E6" s="5">
         <v>2</v>
@@ -1575,10 +1575,10 @@
         <v>55</v>
       </c>
       <c r="C7">
-        <v>3966</v>
+        <v>5364</v>
       </c>
       <c r="D7">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="E7" s="5">
         <v>2</v>
@@ -1592,10 +1592,10 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>4303</v>
+        <v>5674</v>
       </c>
       <c r="D8">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E8" s="5">
         <v>2</v>
@@ -1609,10 +1609,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>3548</v>
+        <v>4564</v>
       </c>
       <c r="D9">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="E9" s="5">
         <v>3</v>
@@ -1626,10 +1626,10 @@
         <v>54</v>
       </c>
       <c r="C10">
-        <v>3067</v>
+        <v>4087</v>
       </c>
       <c r="D10">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="E10" s="5">
         <v>3</v>
@@ -1643,10 +1643,10 @@
         <v>55</v>
       </c>
       <c r="C11">
-        <v>3016</v>
+        <v>3966</v>
       </c>
       <c r="D11">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="E11" s="5">
         <v>4</v>
@@ -1660,10 +1660,10 @@
         <v>56</v>
       </c>
       <c r="C12">
-        <v>3190</v>
+        <v>4361</v>
       </c>
       <c r="D12">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="E12" s="5">
         <v>4</v>
@@ -1677,10 +1677,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>2441</v>
+        <v>3293</v>
       </c>
       <c r="D13">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="E13" s="5">
         <v>4</v>
@@ -1694,10 +1694,10 @@
         <v>54</v>
       </c>
       <c r="C14">
-        <v>2300</v>
+        <v>3031</v>
       </c>
       <c r="D14">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="E14" s="5">
         <v>5</v>
@@ -1711,10 +1711,10 @@
         <v>55</v>
       </c>
       <c r="C15">
-        <v>2200</v>
+        <v>2905</v>
       </c>
       <c r="D15">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E15" s="5">
         <v>6</v>
@@ -1728,10 +1728,10 @@
         <v>56</v>
       </c>
       <c r="C16">
-        <v>2326</v>
+        <v>3257</v>
       </c>
       <c r="D16">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="E16" s="5">
         <v>5</v>
@@ -1745,10 +1745,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1678</v>
+        <v>2293</v>
       </c>
       <c r="D17">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E17" s="5">
         <v>6</v>
@@ -1762,10 +1762,10 @@
         <v>54</v>
       </c>
       <c r="C18">
-        <v>1541</v>
+        <v>1967</v>
       </c>
       <c r="D18">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="E18" s="5">
         <v>7</v>
@@ -1779,10 +1779,10 @@
         <v>55</v>
       </c>
       <c r="C19">
-        <v>1483</v>
+        <v>1884</v>
       </c>
       <c r="D19">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E19" s="5">
         <v>6</v>
@@ -1796,10 +1796,10 @@
         <v>56</v>
       </c>
       <c r="C20">
-        <v>1666</v>
+        <v>1959</v>
       </c>
       <c r="D20">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="E20" s="5">
         <v>8</v>
@@ -1853,10 +1853,10 @@
         <v>67</v>
       </c>
       <c r="C5" s="10">
-        <v>184847.5</v>
+        <v>249236</v>
       </c>
       <c r="D5" s="11">
-        <v>284155</v>
+        <v>384430</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1867,10 +1867,10 @@
         <v>69</v>
       </c>
       <c r="C6" s="10">
-        <v>176719.6</v>
+        <v>235701.2</v>
       </c>
       <c r="D6" s="11">
-        <v>275837</v>
+        <v>368225</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1881,10 +1881,10 @@
         <v>71</v>
       </c>
       <c r="C7" s="10">
-        <v>309372</v>
+        <v>408294</v>
       </c>
       <c r="D7" s="11">
-        <v>411485</v>
+        <v>543525</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1895,10 +1895,10 @@
         <v>73</v>
       </c>
       <c r="C8" s="10">
-        <v>124630.3</v>
+        <v>156154.3</v>
       </c>
       <c r="D8" s="11">
-        <v>184942</v>
+        <v>231845</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1909,10 +1909,10 @@
         <v>75</v>
       </c>
       <c r="C9" s="10">
-        <v>101506.8</v>
+        <v>134301.3</v>
       </c>
       <c r="D9" s="11">
-        <v>151463</v>
+        <v>200421</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1923,10 +1923,10 @@
         <v>77</v>
       </c>
       <c r="C10" s="10">
-        <v>283991</v>
+        <v>370231</v>
       </c>
       <c r="D10" s="11">
-        <v>362901</v>
+        <v>473009</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1937,10 +1937,10 @@
         <v>79</v>
       </c>
       <c r="C11" s="10">
-        <v>75789</v>
+        <v>115878</v>
       </c>
       <c r="D11" s="11">
-        <v>112168</v>
+        <v>171499</v>
       </c>
     </row>
   </sheetData>
@@ -1991,10 +1991,10 @@
         <v>86</v>
       </c>
       <c r="C5">
-        <v>709</v>
+        <v>879</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6899999999999999</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2005,10 +2005,10 @@
         <v>87</v>
       </c>
       <c r="C6">
-        <v>561</v>
+        <v>868</v>
       </c>
       <c r="D6" s="4">
-        <v>0.7240000000000001</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2019,10 +2019,10 @@
         <v>88</v>
       </c>
       <c r="C7">
-        <v>478</v>
+        <v>603</v>
       </c>
       <c r="D7" s="4">
-        <v>0.789</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2033,10 +2033,10 @@
         <v>89</v>
       </c>
       <c r="C8">
-        <v>568</v>
+        <v>707</v>
       </c>
       <c r="D8" s="4">
-        <v>0.8079999999999999</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2047,10 +2047,10 @@
         <v>86</v>
       </c>
       <c r="C9">
-        <v>538</v>
+        <v>671</v>
       </c>
       <c r="D9" s="4">
-        <v>0.701</v>
+        <v>0.6809999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2061,10 +2061,10 @@
         <v>87</v>
       </c>
       <c r="C10">
-        <v>456</v>
+        <v>614</v>
       </c>
       <c r="D10" s="4">
-        <v>0.741</v>
+        <v>0.7390000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2075,10 +2075,10 @@
         <v>88</v>
       </c>
       <c r="C11">
-        <v>331</v>
+        <v>445</v>
       </c>
       <c r="D11" s="4">
-        <v>0.8009999999999999</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2089,10 +2089,10 @@
         <v>89</v>
       </c>
       <c r="C12">
-        <v>391</v>
+        <v>513</v>
       </c>
       <c r="D12" s="4">
-        <v>0.79</v>
+        <v>0.8270000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2103,10 +2103,10 @@
         <v>86</v>
       </c>
       <c r="C13">
-        <v>244</v>
+        <v>306</v>
       </c>
       <c r="D13" s="4">
-        <v>0.6970000000000001</v>
+        <v>0.7090000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2117,10 +2117,10 @@
         <v>87</v>
       </c>
       <c r="C14">
-        <v>212</v>
+        <v>308</v>
       </c>
       <c r="D14" s="4">
-        <v>0.708</v>
+        <v>0.7559999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2131,10 +2131,10 @@
         <v>88</v>
       </c>
       <c r="C15">
-        <v>123</v>
+        <v>214</v>
       </c>
       <c r="D15" s="4">
-        <v>0.797</v>
+        <v>0.8220000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2145,10 +2145,10 @@
         <v>89</v>
       </c>
       <c r="C16">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="D16" s="4">
-        <v>0.82</v>
+        <v>0.726</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2159,10 +2159,10 @@
         <v>86</v>
       </c>
       <c r="C17">
-        <v>296</v>
+        <v>448</v>
       </c>
       <c r="D17" s="4">
-        <v>0.659</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2173,10 +2173,10 @@
         <v>87</v>
       </c>
       <c r="C18">
-        <v>272</v>
+        <v>377</v>
       </c>
       <c r="D18" s="4">
-        <v>0.746</v>
+        <v>0.777</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2187,10 +2187,10 @@
         <v>88</v>
       </c>
       <c r="C19">
-        <v>221</v>
+        <v>278</v>
       </c>
       <c r="D19" s="4">
-        <v>0.787</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2201,10 +2201,10 @@
         <v>89</v>
       </c>
       <c r="C20">
-        <v>243</v>
+        <v>304</v>
       </c>
       <c r="D20" s="4">
-        <v>0.728</v>
+        <v>0.763</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2215,10 +2215,10 @@
         <v>86</v>
       </c>
       <c r="C21">
-        <v>440</v>
+        <v>563</v>
       </c>
       <c r="D21" s="4">
-        <v>0.63</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2229,10 +2229,10 @@
         <v>87</v>
       </c>
       <c r="C22">
-        <v>444</v>
+        <v>517</v>
       </c>
       <c r="D22" s="4">
-        <v>0.782</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2243,10 +2243,10 @@
         <v>88</v>
       </c>
       <c r="C23">
-        <v>282</v>
+        <v>397</v>
       </c>
       <c r="D23" s="4">
-        <v>0.752</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2257,10 +2257,10 @@
         <v>89</v>
       </c>
       <c r="C24">
-        <v>379</v>
+        <v>448</v>
       </c>
       <c r="D24" s="4">
-        <v>0.799</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2271,10 +2271,10 @@
         <v>86</v>
       </c>
       <c r="C25">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D25" s="4">
-        <v>0.723</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2285,10 +2285,10 @@
         <v>87</v>
       </c>
       <c r="C26">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D26" s="4">
-        <v>0.696</v>
+        <v>0.7240000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2299,10 +2299,10 @@
         <v>88</v>
       </c>
       <c r="C27">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D27" s="4">
-        <v>0.7829999999999999</v>
+        <v>0.925</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2313,10 +2313,10 @@
         <v>89</v>
       </c>
       <c r="C28">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D28" s="4">
-        <v>0.7</v>
+        <v>0.7829999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/task193/golden/sequence_screen_2027Q1.xlsx
+++ b/task193/golden/sequence_screen_2027Q1.xlsx
@@ -156,7 +156,7 @@
     <t>Pairs below the 25-patient minimum are shown with no figures and are carried forward to the next run under section 3.4.</t>
   </si>
   <si>
-    <t>Nearest pair on the wrong side of the line: Dalvextin and acid-suppressant, multiple 1.07.</t>
+    <t>Nearest pair on the wrong side of the line: Dalvextin and acid-suppressant, multiple 1.02.</t>
   </si>
   <si>
     <t>Dispensing lines by chain and quarter of dispensing</t>
@@ -773,22 +773,22 @@
         <v>15</v>
       </c>
       <c r="D6">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="E6">
+        <v>96</v>
+      </c>
+      <c r="F6">
         <v>93</v>
       </c>
-      <c r="F6">
-        <v>89</v>
-      </c>
       <c r="G6" s="4">
-        <v>0.511</v>
+        <v>0.508</v>
       </c>
       <c r="H6" s="5">
-        <v>86.7</v>
+        <v>93.7</v>
       </c>
       <c r="I6" s="6">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="J6" t="s">
         <v>16</v>
@@ -805,22 +805,22 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E7">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F7">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G7" s="4">
-        <v>0.5479999999999999</v>
+        <v>0.539</v>
       </c>
       <c r="H7" s="5">
-        <v>103.6</v>
+        <v>113.1</v>
       </c>
       <c r="I7" s="6">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
@@ -837,22 +837,22 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E8">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F8">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G8" s="4">
-        <v>0.727</v>
+        <v>0.71</v>
       </c>
       <c r="H8" s="5">
-        <v>170.4</v>
+        <v>171.2</v>
       </c>
       <c r="I8" s="6">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -869,22 +869,22 @@
         <v>15</v>
       </c>
       <c r="D9">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E9">
         <v>246</v>
       </c>
       <c r="F9">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G9" s="4">
-        <v>0.728</v>
+        <v>0.732</v>
       </c>
       <c r="H9" s="5">
-        <v>175.1</v>
+        <v>176.8</v>
       </c>
       <c r="I9" s="6">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -901,22 +901,22 @@
         <v>22</v>
       </c>
       <c r="D10">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E10">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F10">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G10" s="4">
-        <v>0.551</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H10" s="5">
-        <v>97.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I10" s="6">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="J10" t="s">
         <v>16</v>
@@ -933,22 +933,22 @@
         <v>23</v>
       </c>
       <c r="D11">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="E11">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F11">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G11" s="4">
-        <v>0.539</v>
+        <v>0.529</v>
       </c>
       <c r="H11" s="5">
-        <v>87.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="I11" s="6">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="J11" t="s">
         <v>16</v>
@@ -965,22 +965,22 @@
         <v>26</v>
       </c>
       <c r="D12">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="E12">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F12">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="G12" s="4">
-        <v>0.202</v>
+        <v>0.203</v>
       </c>
       <c r="H12" s="5">
-        <v>73.09999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I12" s="6">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="J12" t="s">
         <v>16</v>
@@ -997,22 +997,22 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="E13">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F13">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G13" s="4">
-        <v>0.509</v>
+        <v>0.499</v>
       </c>
       <c r="H13" s="5">
-        <v>195.2</v>
+        <v>195.5</v>
       </c>
       <c r="I13" s="6">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -1029,19 +1029,19 @@
         <v>23</v>
       </c>
       <c r="D14">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="E14">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F14">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="G14" s="4">
-        <v>0.212</v>
+        <v>0.215</v>
       </c>
       <c r="H14" s="5">
-        <v>74.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I14" s="6">
         <v>0.96</v>
@@ -1061,19 +1061,19 @@
         <v>18</v>
       </c>
       <c r="D15">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="E15">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F15">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="G15" s="4">
-        <v>0.326</v>
+        <v>0.348</v>
       </c>
       <c r="H15" s="5">
-        <v>142.6</v>
+        <v>146.5</v>
       </c>
       <c r="I15" s="6">
         <v>1</v>
@@ -1093,22 +1093,22 @@
         <v>22</v>
       </c>
       <c r="D16">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="E16">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="F16">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="G16" s="4">
-        <v>0.58</v>
+        <v>0.551</v>
       </c>
       <c r="H16" s="5">
-        <v>290.6</v>
+        <v>280.9</v>
       </c>
       <c r="I16" s="6">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
@@ -1125,22 +1125,22 @@
         <v>29</v>
       </c>
       <c r="D17">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="E17">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="F17">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="G17" s="4">
-        <v>0.279</v>
+        <v>0.298</v>
       </c>
       <c r="H17" s="5">
-        <v>137.6</v>
+        <v>142</v>
       </c>
       <c r="I17" s="6">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="J17" t="s">
         <v>16</v>
@@ -1157,22 +1157,22 @@
         <v>26</v>
       </c>
       <c r="D18">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="E18">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="F18">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G18" s="4">
-        <v>0.8159999999999999</v>
+        <v>0.821</v>
       </c>
       <c r="H18" s="5">
-        <v>215.9</v>
+        <v>230.1</v>
       </c>
       <c r="I18" s="6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="J18" t="s">
         <v>16</v>
@@ -1189,22 +1189,22 @@
         <v>15</v>
       </c>
       <c r="D19">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="E19">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F19">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G19" s="4">
-        <v>0.77</v>
+        <v>0.758</v>
       </c>
       <c r="H19" s="5">
-        <v>224.8</v>
+        <v>230.7</v>
       </c>
       <c r="I19" s="6">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="J19" t="s">
         <v>16</v>
@@ -1221,16 +1221,16 @@
         <v>23</v>
       </c>
       <c r="D20">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E20">
         <v>210</v>
       </c>
       <c r="F20">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G20" s="4">
-        <v>0.784</v>
+        <v>0.7809999999999999</v>
       </c>
       <c r="H20" s="5">
         <v>210.1</v>
@@ -1253,19 +1253,19 @@
         <v>26</v>
       </c>
       <c r="D21">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E21">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F21">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G21" s="4">
-        <v>0.728</v>
+        <v>0.727</v>
       </c>
       <c r="H21" s="5">
-        <v>215.8</v>
+        <v>216.9</v>
       </c>
       <c r="I21" s="6">
         <v>1.46</v>
@@ -1285,13 +1285,13 @@
         <v>34</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" t="s">
         <v>35</v>
@@ -1308,22 +1308,22 @@
         <v>23</v>
       </c>
       <c r="D23">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="E23">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="F23">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="G23" s="4">
-        <v>0.757</v>
+        <v>0.738</v>
       </c>
       <c r="H23" s="5">
-        <v>148.4</v>
+        <v>163.5</v>
       </c>
       <c r="I23" s="6">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
@@ -1340,10 +1340,10 @@
         <v>34</v>
       </c>
       <c r="D24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24">
         <v>6</v>
@@ -1363,19 +1363,19 @@
         <v>18</v>
       </c>
       <c r="D25">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E25">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F25">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G25" s="4">
-        <v>0.769</v>
+        <v>0.7609999999999999</v>
       </c>
       <c r="H25" s="5">
-        <v>166.1</v>
+        <v>162.4</v>
       </c>
       <c r="I25" s="6">
         <v>1</v>
@@ -1395,22 +1395,22 @@
         <v>22</v>
       </c>
       <c r="D26">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="E26">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="F26">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G26" s="4">
-        <v>0.7879999999999999</v>
+        <v>0.8009999999999999</v>
       </c>
       <c r="H26" s="5">
-        <v>195.9</v>
+        <v>210.4</v>
       </c>
       <c r="I26" s="6">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="J26" t="s">
         <v>16</v>
@@ -1427,22 +1427,22 @@
         <v>29</v>
       </c>
       <c r="D27">
-        <v>556</v>
+        <v>536</v>
       </c>
       <c r="E27">
-        <v>430</v>
+        <v>401</v>
       </c>
       <c r="F27">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G27" s="4">
-        <v>0.773</v>
+        <v>0.748</v>
       </c>
       <c r="H27" s="5">
-        <v>298.8</v>
+        <v>289.7</v>
       </c>
       <c r="I27" s="6">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
@@ -1459,13 +1459,13 @@
         <v>34</v>
       </c>
       <c r="D28">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E28">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J28" t="s">
         <v>35</v>
@@ -1541,10 +1541,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>5869</v>
+        <v>5882</v>
       </c>
       <c r="D5">
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -1558,10 +1558,10 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>5325</v>
+        <v>5453</v>
       </c>
       <c r="D6">
-        <v>184</v>
+        <v>54</v>
       </c>
       <c r="E6" s="5">
         <v>2</v>
@@ -1575,10 +1575,10 @@
         <v>55</v>
       </c>
       <c r="C7">
-        <v>5364</v>
+        <v>5499</v>
       </c>
       <c r="D7">
-        <v>167</v>
+        <v>43</v>
       </c>
       <c r="E7" s="5">
         <v>2</v>
@@ -1592,10 +1592,10 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>5674</v>
+        <v>5661</v>
       </c>
       <c r="D8">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="E8" s="5">
         <v>2</v>
@@ -1609,10 +1609,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>4564</v>
+        <v>4620</v>
       </c>
       <c r="D9">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="E9" s="5">
         <v>3</v>
@@ -1626,10 +1626,10 @@
         <v>54</v>
       </c>
       <c r="C10">
-        <v>4087</v>
+        <v>4167</v>
       </c>
       <c r="D10">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="E10" s="5">
         <v>3</v>
@@ -1643,10 +1643,10 @@
         <v>55</v>
       </c>
       <c r="C11">
-        <v>3966</v>
+        <v>4137</v>
       </c>
       <c r="D11">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="E11" s="5">
         <v>4</v>
@@ -1660,10 +1660,10 @@
         <v>56</v>
       </c>
       <c r="C12">
-        <v>4361</v>
+        <v>4379</v>
       </c>
       <c r="D12">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="E12" s="5">
         <v>4</v>
@@ -1677,10 +1677,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>3293</v>
+        <v>3343</v>
       </c>
       <c r="D13">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="E13" s="5">
         <v>4</v>
@@ -1694,10 +1694,10 @@
         <v>54</v>
       </c>
       <c r="C14">
-        <v>3031</v>
+        <v>3059</v>
       </c>
       <c r="D14">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E14" s="5">
         <v>5</v>
@@ -1711,10 +1711,10 @@
         <v>55</v>
       </c>
       <c r="C15">
-        <v>2905</v>
+        <v>2895</v>
       </c>
       <c r="D15">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E15" s="5">
         <v>6</v>
@@ -1728,13 +1728,13 @@
         <v>56</v>
       </c>
       <c r="C16">
-        <v>3257</v>
+        <v>3204</v>
       </c>
       <c r="D16">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="E16" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1745,10 +1745,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>2293</v>
+        <v>2244</v>
       </c>
       <c r="D17">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="E17" s="5">
         <v>6</v>
@@ -1762,10 +1762,10 @@
         <v>54</v>
       </c>
       <c r="C18">
-        <v>1967</v>
+        <v>1984</v>
       </c>
       <c r="D18">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="E18" s="5">
         <v>7</v>
@@ -1779,10 +1779,10 @@
         <v>55</v>
       </c>
       <c r="C19">
-        <v>1884</v>
+        <v>1940</v>
       </c>
       <c r="D19">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E19" s="5">
         <v>6</v>
@@ -1796,10 +1796,10 @@
         <v>56</v>
       </c>
       <c r="C20">
-        <v>1959</v>
+        <v>2003</v>
       </c>
       <c r="D20">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E20" s="5">
         <v>8</v>
@@ -1853,10 +1853,10 @@
         <v>67</v>
       </c>
       <c r="C5" s="10">
-        <v>249236</v>
+        <v>256094.5</v>
       </c>
       <c r="D5" s="11">
-        <v>384430</v>
+        <v>329786</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1867,10 +1867,10 @@
         <v>69</v>
       </c>
       <c r="C6" s="10">
-        <v>235701.2</v>
+        <v>233630.2</v>
       </c>
       <c r="D6" s="11">
-        <v>368225</v>
+        <v>364993</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1881,10 +1881,10 @@
         <v>71</v>
       </c>
       <c r="C7" s="10">
-        <v>408294</v>
+        <v>407568</v>
       </c>
       <c r="D7" s="11">
-        <v>543525</v>
+        <v>542674</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1895,10 +1895,10 @@
         <v>73</v>
       </c>
       <c r="C8" s="10">
-        <v>156154.3</v>
+        <v>159687.8</v>
       </c>
       <c r="D8" s="11">
-        <v>231845</v>
+        <v>236990</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1909,10 +1909,10 @@
         <v>75</v>
       </c>
       <c r="C9" s="10">
-        <v>134301.3</v>
+        <v>80303.2</v>
       </c>
       <c r="D9" s="11">
-        <v>200421</v>
+        <v>120540</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1923,10 +1923,10 @@
         <v>77</v>
       </c>
       <c r="C10" s="10">
-        <v>370231</v>
+        <v>315988</v>
       </c>
       <c r="D10" s="11">
-        <v>473009</v>
+        <v>400858</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1937,10 +1937,10 @@
         <v>79</v>
       </c>
       <c r="C11" s="10">
-        <v>115878</v>
+        <v>114198</v>
       </c>
       <c r="D11" s="11">
-        <v>171499</v>
+        <v>169013</v>
       </c>
     </row>
   </sheetData>
@@ -1991,10 +1991,10 @@
         <v>86</v>
       </c>
       <c r="C5">
-        <v>879</v>
+        <v>868</v>
       </c>
       <c r="D5" s="4">
-        <v>0.669</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2005,10 +2005,10 @@
         <v>87</v>
       </c>
       <c r="C6">
-        <v>868</v>
+        <v>787</v>
       </c>
       <c r="D6" s="4">
-        <v>0.75</v>
+        <v>0.778</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2019,10 +2019,10 @@
         <v>88</v>
       </c>
       <c r="C7">
-        <v>603</v>
+        <v>551</v>
       </c>
       <c r="D7" s="4">
-        <v>0.769</v>
+        <v>0.8079999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2033,10 +2033,10 @@
         <v>89</v>
       </c>
       <c r="C8">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D8" s="4">
-        <v>0.779</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2047,10 +2047,10 @@
         <v>86</v>
       </c>
       <c r="C9">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="D9" s="4">
-        <v>0.6809999999999999</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2061,10 +2061,10 @@
         <v>87</v>
       </c>
       <c r="C10">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="D10" s="4">
-        <v>0.7390000000000001</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2075,10 +2075,10 @@
         <v>88</v>
       </c>
       <c r="C11">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="D11" s="4">
-        <v>0.787</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2089,10 +2089,10 @@
         <v>89</v>
       </c>
       <c r="C12">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="D12" s="4">
-        <v>0.8270000000000001</v>
+        <v>0.767</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2103,10 +2103,10 @@
         <v>86</v>
       </c>
       <c r="C13">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D13" s="4">
-        <v>0.7090000000000001</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2117,10 +2117,10 @@
         <v>87</v>
       </c>
       <c r="C14">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="D14" s="4">
-        <v>0.7559999999999999</v>
+        <v>0.758</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2131,10 +2131,10 @@
         <v>88</v>
       </c>
       <c r="C15">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="D15" s="4">
-        <v>0.8220000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2145,10 +2145,10 @@
         <v>89</v>
       </c>
       <c r="C16">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="D16" s="4">
-        <v>0.726</v>
+        <v>0.8059999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2159,10 +2159,10 @@
         <v>86</v>
       </c>
       <c r="C17">
-        <v>448</v>
+        <v>391</v>
       </c>
       <c r="D17" s="4">
-        <v>0.703</v>
+        <v>0.726</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2173,10 +2173,10 @@
         <v>87</v>
       </c>
       <c r="C18">
-        <v>377</v>
+        <v>422</v>
       </c>
       <c r="D18" s="4">
-        <v>0.777</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2187,10 +2187,10 @@
         <v>88</v>
       </c>
       <c r="C19">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="D19" s="4">
-        <v>0.802</v>
+        <v>0.789</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2201,10 +2201,10 @@
         <v>89</v>
       </c>
       <c r="C20">
-        <v>304</v>
+        <v>338</v>
       </c>
       <c r="D20" s="4">
-        <v>0.763</v>
+        <v>0.8079999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2215,10 +2215,10 @@
         <v>86</v>
       </c>
       <c r="C21">
-        <v>563</v>
+        <v>621</v>
       </c>
       <c r="D21" s="4">
-        <v>0.6870000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2229,10 +2229,10 @@
         <v>87</v>
       </c>
       <c r="C22">
-        <v>517</v>
+        <v>550</v>
       </c>
       <c r="D22" s="4">
-        <v>0.772</v>
+        <v>0.7490000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2243,10 +2243,10 @@
         <v>88</v>
       </c>
       <c r="C23">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="D23" s="4">
-        <v>0.826</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2257,10 +2257,10 @@
         <v>89</v>
       </c>
       <c r="C24">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="D24" s="4">
-        <v>0.8120000000000001</v>
+        <v>0.795</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2271,10 +2271,10 @@
         <v>86</v>
       </c>
       <c r="C25">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="D25" s="4">
-        <v>0.703</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2285,10 +2285,10 @@
         <v>87</v>
       </c>
       <c r="C26">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D26" s="4">
-        <v>0.7240000000000001</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2299,10 +2299,10 @@
         <v>88</v>
       </c>
       <c r="C27">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D27" s="4">
-        <v>0.925</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2313,10 +2313,10 @@
         <v>89</v>
       </c>
       <c r="C28">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D28" s="4">
-        <v>0.7829999999999999</v>
+        <v>0.804</v>
       </c>
     </row>
   </sheetData>

--- a/task193/golden/sequence_screen_2027Q1.xlsx
+++ b/task193/golden/sequence_screen_2027Q1.xlsx
@@ -156,7 +156,7 @@
     <t>Pairs below the 25-patient minimum are shown with no figures and are carried forward to the next run under section 3.4.</t>
   </si>
   <si>
-    <t>Nearest pair on the wrong side of the line: Dalvextin and acid-suppressant, multiple 1.02.</t>
+    <t>Nearest pair on the wrong side of the line: Dalvextin and acid-suppressant, multiple 1.03.</t>
   </si>
   <si>
     <t>Dispensing lines by chain and quarter of dispensing</t>
@@ -773,22 +773,22 @@
         <v>15</v>
       </c>
       <c r="D6">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="E6">
+        <v>99</v>
+      </c>
+      <c r="F6">
         <v>96</v>
-      </c>
-      <c r="F6">
-        <v>93</v>
       </c>
       <c r="G6" s="4">
         <v>0.508</v>
       </c>
       <c r="H6" s="5">
-        <v>93.7</v>
+        <v>95.8</v>
       </c>
       <c r="I6" s="6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="J6" t="s">
         <v>16</v>
@@ -817,10 +817,10 @@
         <v>0.539</v>
       </c>
       <c r="H7" s="5">
-        <v>113.1</v>
+        <v>112.7</v>
       </c>
       <c r="I7" s="6">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
@@ -837,22 +837,22 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>338</v>
+        <v>375</v>
       </c>
       <c r="E8">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="F8">
         <v>98</v>
       </c>
       <c r="G8" s="4">
-        <v>0.71</v>
+        <v>0.7390000000000001</v>
       </c>
       <c r="H8" s="5">
-        <v>171.2</v>
+        <v>187.5</v>
       </c>
       <c r="I8" s="6">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -869,22 +869,22 @@
         <v>15</v>
       </c>
       <c r="D9">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="E9">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="F9">
         <v>90</v>
       </c>
       <c r="G9" s="4">
-        <v>0.732</v>
+        <v>0.752</v>
       </c>
       <c r="H9" s="5">
-        <v>176.8</v>
+        <v>188.1</v>
       </c>
       <c r="I9" s="6">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -901,19 +901,19 @@
         <v>22</v>
       </c>
       <c r="D10">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E10">
         <v>94</v>
       </c>
       <c r="F10">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G10" s="4">
-        <v>0.5600000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="H10" s="5">
-        <v>93.90000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="I10" s="6">
         <v>1</v>
@@ -933,22 +933,22 @@
         <v>23</v>
       </c>
       <c r="D11">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E11">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F11">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G11" s="4">
         <v>0.529</v>
       </c>
       <c r="H11" s="5">
-        <v>92.5</v>
+        <v>92.7</v>
       </c>
       <c r="I11" s="6">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="J11" t="s">
         <v>16</v>
@@ -965,22 +965,22 @@
         <v>26</v>
       </c>
       <c r="D12">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E12">
         <v>71</v>
       </c>
       <c r="F12">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G12" s="4">
-        <v>0.203</v>
+        <v>0.205</v>
       </c>
       <c r="H12" s="5">
-        <v>75.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I12" s="6">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="J12" t="s">
         <v>16</v>
@@ -997,22 +997,22 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E13">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F13">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G13" s="4">
-        <v>0.499</v>
+        <v>0.491</v>
       </c>
       <c r="H13" s="5">
-        <v>195.5</v>
+        <v>196.2</v>
       </c>
       <c r="I13" s="6">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -1029,22 +1029,22 @@
         <v>23</v>
       </c>
       <c r="D14">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E14">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F14">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G14" s="4">
-        <v>0.215</v>
+        <v>0.194</v>
       </c>
       <c r="H14" s="5">
-        <v>74.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I14" s="6">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="J14" t="s">
         <v>16</v>
@@ -1073,7 +1073,7 @@
         <v>0.348</v>
       </c>
       <c r="H15" s="5">
-        <v>146.5</v>
+        <v>147.3</v>
       </c>
       <c r="I15" s="6">
         <v>1</v>
@@ -1093,19 +1093,19 @@
         <v>22</v>
       </c>
       <c r="D16">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E16">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F16">
         <v>311</v>
       </c>
       <c r="G16" s="4">
-        <v>0.551</v>
+        <v>0.552</v>
       </c>
       <c r="H16" s="5">
-        <v>280.9</v>
+        <v>280.7</v>
       </c>
       <c r="I16" s="6">
         <v>1.36</v>
@@ -1125,19 +1125,19 @@
         <v>29</v>
       </c>
       <c r="D17">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="E17">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F17">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="G17" s="4">
-        <v>0.298</v>
+        <v>0.285</v>
       </c>
       <c r="H17" s="5">
-        <v>142</v>
+        <v>140.7</v>
       </c>
       <c r="I17" s="6">
         <v>1.02</v>
@@ -1160,19 +1160,19 @@
         <v>279</v>
       </c>
       <c r="E18">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F18">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G18" s="4">
-        <v>0.821</v>
+        <v>0.8140000000000001</v>
       </c>
       <c r="H18" s="5">
-        <v>230.1</v>
+        <v>229.5</v>
       </c>
       <c r="I18" s="6">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="J18" t="s">
         <v>16</v>
@@ -1189,19 +1189,19 @@
         <v>15</v>
       </c>
       <c r="D19">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E19">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F19">
         <v>72</v>
       </c>
       <c r="G19" s="4">
-        <v>0.758</v>
+        <v>0.7609999999999999</v>
       </c>
       <c r="H19" s="5">
-        <v>230.7</v>
+        <v>234.7</v>
       </c>
       <c r="I19" s="6">
         <v>0.98</v>
@@ -1224,19 +1224,19 @@
         <v>269</v>
       </c>
       <c r="E20">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F20">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G20" s="4">
-        <v>0.7809999999999999</v>
+        <v>0.773</v>
       </c>
       <c r="H20" s="5">
-        <v>210.1</v>
+        <v>209.3</v>
       </c>
       <c r="I20" s="6">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="J20" t="s">
         <v>16</v>
@@ -1253,22 +1253,22 @@
         <v>26</v>
       </c>
       <c r="D21">
-        <v>436</v>
+        <v>480</v>
       </c>
       <c r="E21">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="F21">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="G21" s="4">
-        <v>0.727</v>
+        <v>0.721</v>
       </c>
       <c r="H21" s="5">
-        <v>216.9</v>
+        <v>232.2</v>
       </c>
       <c r="I21" s="6">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="J21" t="s">
         <v>19</v>
@@ -1288,10 +1288,10 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J22" t="s">
         <v>35</v>
@@ -1308,22 +1308,22 @@
         <v>23</v>
       </c>
       <c r="D23">
-        <v>294</v>
+        <v>339</v>
       </c>
       <c r="E23">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="F23">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G23" s="4">
-        <v>0.738</v>
+        <v>0.743</v>
       </c>
       <c r="H23" s="5">
-        <v>163.5</v>
+        <v>180.2</v>
       </c>
       <c r="I23" s="6">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
@@ -1363,19 +1363,19 @@
         <v>18</v>
       </c>
       <c r="D25">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E25">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F25">
         <v>51</v>
       </c>
       <c r="G25" s="4">
-        <v>0.7609999999999999</v>
+        <v>0.757</v>
       </c>
       <c r="H25" s="5">
-        <v>162.4</v>
+        <v>159.4</v>
       </c>
       <c r="I25" s="6">
         <v>1</v>
@@ -1395,19 +1395,19 @@
         <v>22</v>
       </c>
       <c r="D26">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E26">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F26">
         <v>53</v>
       </c>
       <c r="G26" s="4">
-        <v>0.8009999999999999</v>
+        <v>0.802</v>
       </c>
       <c r="H26" s="5">
-        <v>210.4</v>
+        <v>211.2</v>
       </c>
       <c r="I26" s="6">
         <v>1.02</v>
@@ -1427,22 +1427,22 @@
         <v>29</v>
       </c>
       <c r="D27">
-        <v>536</v>
+        <v>631</v>
       </c>
       <c r="E27">
-        <v>401</v>
+        <v>496</v>
       </c>
       <c r="F27">
         <v>135</v>
       </c>
       <c r="G27" s="4">
-        <v>0.748</v>
+        <v>0.7859999999999999</v>
       </c>
       <c r="H27" s="5">
-        <v>289.7</v>
+        <v>330.9</v>
       </c>
       <c r="I27" s="6">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
@@ -1462,10 +1462,10 @@
         <v>17</v>
       </c>
       <c r="E28">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" t="s">
         <v>35</v>
@@ -1541,10 +1541,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>5882</v>
+        <v>5985</v>
       </c>
       <c r="D5">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -1558,10 +1558,10 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>5453</v>
+        <v>5476</v>
       </c>
       <c r="D6">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E6" s="5">
         <v>2</v>
@@ -1575,10 +1575,10 @@
         <v>55</v>
       </c>
       <c r="C7">
-        <v>5499</v>
+        <v>5554</v>
       </c>
       <c r="D7">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" s="5">
         <v>2</v>
@@ -1592,10 +1592,10 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>5661</v>
+        <v>5732</v>
       </c>
       <c r="D8">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E8" s="5">
         <v>2</v>
@@ -1609,10 +1609,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>4620</v>
+        <v>4673</v>
       </c>
       <c r="D9">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E9" s="5">
         <v>3</v>
@@ -1626,10 +1626,10 @@
         <v>54</v>
       </c>
       <c r="C10">
-        <v>4167</v>
+        <v>4119</v>
       </c>
       <c r="D10">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E10" s="5">
         <v>3</v>
@@ -1643,10 +1643,10 @@
         <v>55</v>
       </c>
       <c r="C11">
-        <v>4137</v>
+        <v>4082</v>
       </c>
       <c r="D11">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E11" s="5">
         <v>4</v>
@@ -1660,10 +1660,10 @@
         <v>56</v>
       </c>
       <c r="C12">
-        <v>4379</v>
+        <v>4344</v>
       </c>
       <c r="D12">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E12" s="5">
         <v>4</v>
@@ -1677,10 +1677,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>3343</v>
+        <v>3386</v>
       </c>
       <c r="D13">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E13" s="5">
         <v>4</v>
@@ -1694,10 +1694,10 @@
         <v>54</v>
       </c>
       <c r="C14">
-        <v>3059</v>
+        <v>3064</v>
       </c>
       <c r="D14">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E14" s="5">
         <v>5</v>
@@ -1711,10 +1711,10 @@
         <v>55</v>
       </c>
       <c r="C15">
-        <v>2895</v>
+        <v>2875</v>
       </c>
       <c r="D15">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E15" s="5">
         <v>6</v>
@@ -1728,10 +1728,10 @@
         <v>56</v>
       </c>
       <c r="C16">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="D16">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E16" s="5">
         <v>6</v>
@@ -1745,10 +1745,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>2244</v>
+        <v>2260</v>
       </c>
       <c r="D17">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E17" s="5">
         <v>6</v>
@@ -1762,10 +1762,10 @@
         <v>54</v>
       </c>
       <c r="C18">
-        <v>1984</v>
+        <v>2002</v>
       </c>
       <c r="D18">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E18" s="5">
         <v>7</v>
@@ -1779,10 +1779,10 @@
         <v>55</v>
       </c>
       <c r="C19">
-        <v>1940</v>
+        <v>1933</v>
       </c>
       <c r="D19">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E19" s="5">
         <v>6</v>
@@ -1796,10 +1796,10 @@
         <v>56</v>
       </c>
       <c r="C20">
-        <v>2003</v>
+        <v>1997</v>
       </c>
       <c r="D20">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E20" s="5">
         <v>8</v>
@@ -1853,10 +1853,10 @@
         <v>67</v>
       </c>
       <c r="C5" s="10">
-        <v>256094.5</v>
+        <v>255520.5</v>
       </c>
       <c r="D5" s="11">
-        <v>329786</v>
+        <v>329175</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1867,10 +1867,10 @@
         <v>69</v>
       </c>
       <c r="C6" s="10">
-        <v>233630.2</v>
+        <v>231565.7</v>
       </c>
       <c r="D6" s="11">
-        <v>364993</v>
+        <v>361748</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1881,10 +1881,10 @@
         <v>71</v>
       </c>
       <c r="C7" s="10">
-        <v>407568</v>
+        <v>407656</v>
       </c>
       <c r="D7" s="11">
-        <v>542674</v>
+        <v>542791</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1895,10 +1895,10 @@
         <v>73</v>
       </c>
       <c r="C8" s="10">
-        <v>159687.8</v>
+        <v>159766.9</v>
       </c>
       <c r="D8" s="11">
-        <v>236990</v>
+        <v>237117</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1909,10 +1909,10 @@
         <v>75</v>
       </c>
       <c r="C9" s="10">
-        <v>80303.2</v>
+        <v>80973.60000000001</v>
       </c>
       <c r="D9" s="11">
-        <v>120540</v>
+        <v>121540</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1923,10 +1923,10 @@
         <v>77</v>
       </c>
       <c r="C10" s="10">
-        <v>315988</v>
+        <v>316685.2</v>
       </c>
       <c r="D10" s="11">
-        <v>400858</v>
+        <v>401744</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1937,10 +1937,10 @@
         <v>79</v>
       </c>
       <c r="C11" s="10">
-        <v>114198</v>
+        <v>113515.5</v>
       </c>
       <c r="D11" s="11">
-        <v>169013</v>
+        <v>168003</v>
       </c>
     </row>
   </sheetData>
@@ -1994,7 +1994,7 @@
         <v>868</v>
       </c>
       <c r="D5" s="4">
-        <v>0.68</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2005,10 +2005,10 @@
         <v>87</v>
       </c>
       <c r="C6">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D6" s="4">
-        <v>0.778</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2019,10 +2019,10 @@
         <v>88</v>
       </c>
       <c r="C7">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D7" s="4">
-        <v>0.8079999999999999</v>
+        <v>0.8190000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2036,7 +2036,7 @@
         <v>709</v>
       </c>
       <c r="D8" s="4">
-        <v>0.797</v>
+        <v>0.795</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2050,7 +2050,7 @@
         <v>667</v>
       </c>
       <c r="D9" s="4">
-        <v>0.672</v>
+        <v>0.6809999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2064,7 +2064,7 @@
         <v>626</v>
       </c>
       <c r="D10" s="4">
-        <v>0.759</v>
+        <v>0.767</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2075,10 +2075,10 @@
         <v>88</v>
       </c>
       <c r="C11">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D11" s="4">
-        <v>0.797</v>
+        <v>0.7959999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2092,7 +2092,7 @@
         <v>529</v>
       </c>
       <c r="D12" s="4">
-        <v>0.767</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2106,7 +2106,7 @@
         <v>303</v>
       </c>
       <c r="D13" s="4">
-        <v>0.667</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2120,7 +2120,7 @@
         <v>285</v>
       </c>
       <c r="D14" s="4">
-        <v>0.758</v>
+        <v>0.7509999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2162,7 +2162,7 @@
         <v>391</v>
       </c>
       <c r="D17" s="4">
-        <v>0.726</v>
+        <v>0.7340000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2176,7 +2176,7 @@
         <v>422</v>
       </c>
       <c r="D18" s="4">
-        <v>0.723</v>
+        <v>0.7390000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2190,7 +2190,7 @@
         <v>303</v>
       </c>
       <c r="D19" s="4">
-        <v>0.789</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2204,7 +2204,7 @@
         <v>338</v>
       </c>
       <c r="D20" s="4">
-        <v>0.8079999999999999</v>
+        <v>0.8109999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2218,7 +2218,7 @@
         <v>621</v>
       </c>
       <c r="D21" s="4">
-        <v>0.6840000000000001</v>
+        <v>0.6990000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2232,7 +2232,7 @@
         <v>550</v>
       </c>
       <c r="D22" s="4">
-        <v>0.7490000000000001</v>
+        <v>0.7559999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2260,7 +2260,7 @@
         <v>420</v>
       </c>
       <c r="D24" s="4">
-        <v>0.795</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2274,7 +2274,7 @@
         <v>74</v>
       </c>
       <c r="D25" s="4">
-        <v>0.73</v>
+        <v>0.743</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2302,7 +2302,7 @@
         <v>53</v>
       </c>
       <c r="D27" s="4">
-        <v>0.774</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">

--- a/task193/golden/sequence_screen_2027Q1.xlsx
+++ b/task193/golden/sequence_screen_2027Q1.xlsx
@@ -1853,10 +1853,10 @@
         <v>67</v>
       </c>
       <c r="C5" s="10">
-        <v>255520.5</v>
+        <v>265159</v>
       </c>
       <c r="D5" s="11">
-        <v>329175</v>
+        <v>342547</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1867,10 +1867,10 @@
         <v>69</v>
       </c>
       <c r="C6" s="10">
-        <v>231565.7</v>
+        <v>402993</v>
       </c>
       <c r="D6" s="11">
-        <v>361748</v>
+        <v>530098</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1884,7 +1884,7 @@
         <v>407656</v>
       </c>
       <c r="D7" s="11">
-        <v>542791</v>
+        <v>544754</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1895,10 +1895,10 @@
         <v>73</v>
       </c>
       <c r="C8" s="10">
-        <v>159766.9</v>
+        <v>383410</v>
       </c>
       <c r="D8" s="11">
-        <v>237117</v>
+        <v>476809</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1909,10 +1909,10 @@
         <v>75</v>
       </c>
       <c r="C9" s="10">
-        <v>80973.60000000001</v>
+        <v>595520</v>
       </c>
       <c r="D9" s="11">
-        <v>121540</v>
+        <v>747311</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1923,10 +1923,10 @@
         <v>77</v>
       </c>
       <c r="C10" s="10">
-        <v>316685.2</v>
+        <v>1027098</v>
       </c>
       <c r="D10" s="11">
-        <v>401744</v>
+        <v>1067868</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1937,10 +1937,10 @@
         <v>79</v>
       </c>
       <c r="C11" s="10">
-        <v>113515.5</v>
+        <v>227031</v>
       </c>
       <c r="D11" s="11">
-        <v>168003</v>
+        <v>332600</v>
       </c>
     </row>
   </sheetData>

--- a/task193/golden/sequence_screen_2027Q1.xlsx
+++ b/task193/golden/sequence_screen_2027Q1.xlsx
@@ -1433,10 +1433,10 @@
         <v>29</v>
       </c>
       <c r="D27">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E27">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F27">
         <v>135</v>
@@ -1445,7 +1445,7 @@
         <v>0.7859999999999999</v>
       </c>
       <c r="H27" s="5">
-        <v>330.9</v>
+        <v>331.4</v>
       </c>
       <c r="I27" s="6">
         <v>1.5</v>
@@ -1550,13 +1550,13 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>5985</v>
+        <v>6801</v>
       </c>
       <c r="D5">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1567,10 +1567,10 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>5476</v>
+        <v>6182</v>
       </c>
       <c r="D6">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E6" s="5">
         <v>5</v>
@@ -1584,10 +1584,10 @@
         <v>55</v>
       </c>
       <c r="C7">
-        <v>5554</v>
+        <v>6303</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" s="5">
         <v>4</v>
@@ -1601,13 +1601,13 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>5732</v>
+        <v>6380</v>
       </c>
       <c r="D8">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E8" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1618,10 +1618,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>4673</v>
+        <v>3758</v>
       </c>
       <c r="D9">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E9" s="5">
         <v>3</v>
@@ -1635,10 +1635,10 @@
         <v>54</v>
       </c>
       <c r="C10">
-        <v>4119</v>
+        <v>3268</v>
       </c>
       <c r="D10">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="E10" s="5">
         <v>4</v>
@@ -1652,10 +1652,10 @@
         <v>55</v>
       </c>
       <c r="C11">
-        <v>4082</v>
+        <v>3233</v>
       </c>
       <c r="D11">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E11" s="5">
         <v>4</v>
@@ -1669,10 +1669,10 @@
         <v>56</v>
       </c>
       <c r="C12">
-        <v>4344</v>
+        <v>3477</v>
       </c>
       <c r="D12">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E12" s="5">
         <v>6</v>
@@ -1686,13 +1686,13 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>3386</v>
+        <v>3474</v>
       </c>
       <c r="D13">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E13" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1703,10 +1703,10 @@
         <v>54</v>
       </c>
       <c r="C14">
-        <v>3064</v>
+        <v>3187</v>
       </c>
       <c r="D14">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E14" s="5">
         <v>4</v>
@@ -1720,13 +1720,13 @@
         <v>55</v>
       </c>
       <c r="C15">
-        <v>2875</v>
+        <v>2982</v>
       </c>
       <c r="D15">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E15" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1737,13 +1737,13 @@
         <v>56</v>
       </c>
       <c r="C16">
-        <v>3203</v>
+        <v>3376</v>
       </c>
       <c r="D16">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E16" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1754,10 +1754,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>2260</v>
+        <v>2272</v>
       </c>
       <c r="D17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" s="5">
         <v>7</v>
@@ -1771,10 +1771,10 @@
         <v>54</v>
       </c>
       <c r="C18">
-        <v>2002</v>
+        <v>2035</v>
       </c>
       <c r="D18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" s="5">
         <v>7</v>
@@ -1788,10 +1788,10 @@
         <v>55</v>
       </c>
       <c r="C19">
-        <v>1933</v>
+        <v>1928</v>
       </c>
       <c r="D19">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E19" s="5">
         <v>7</v>
@@ -1805,13 +1805,13 @@
         <v>56</v>
       </c>
       <c r="C20">
-        <v>1997</v>
+        <v>2039</v>
       </c>
       <c r="D20">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E20" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1862,10 +1862,10 @@
         <v>67</v>
       </c>
       <c r="C5" s="10">
-        <v>265159</v>
+        <v>265803</v>
       </c>
       <c r="D5" s="11">
-        <v>342547</v>
+        <v>343410</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1876,10 +1876,10 @@
         <v>69</v>
       </c>
       <c r="C6" s="10">
-        <v>402993</v>
+        <v>402972</v>
       </c>
       <c r="D6" s="11">
-        <v>530098</v>
+        <v>530069</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1890,10 +1890,10 @@
         <v>71</v>
       </c>
       <c r="C7" s="10">
-        <v>407656</v>
+        <v>407628</v>
       </c>
       <c r="D7" s="11">
-        <v>544754</v>
+        <v>544717</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1904,10 +1904,10 @@
         <v>73</v>
       </c>
       <c r="C8" s="10">
-        <v>383410</v>
+        <v>383670</v>
       </c>
       <c r="D8" s="11">
-        <v>476809</v>
+        <v>477132</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1918,10 +1918,10 @@
         <v>75</v>
       </c>
       <c r="C9" s="10">
-        <v>595520</v>
+        <v>595422</v>
       </c>
       <c r="D9" s="11">
-        <v>747311</v>
+        <v>747180</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1932,10 +1932,10 @@
         <v>77</v>
       </c>
       <c r="C10" s="10">
-        <v>1027098</v>
+        <v>1027964</v>
       </c>
       <c r="D10" s="11">
-        <v>1067868</v>
+        <v>1068764</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1946,10 +1946,10 @@
         <v>79</v>
       </c>
       <c r="C11" s="10">
-        <v>227031</v>
+        <v>227367</v>
       </c>
       <c r="D11" s="11">
-        <v>332600</v>
+        <v>333093</v>
       </c>
     </row>
   </sheetData>
@@ -2000,10 +2000,10 @@
         <v>86</v>
       </c>
       <c r="C5">
-        <v>679</v>
+        <v>638</v>
       </c>
       <c r="D5" s="4">
-        <v>0.695</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2014,10 +2014,10 @@
         <v>87</v>
       </c>
       <c r="C6">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="D6" s="4">
-        <v>0.7040000000000001</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2028,10 +2028,10 @@
         <v>88</v>
       </c>
       <c r="C7">
-        <v>779</v>
+        <v>734</v>
       </c>
       <c r="D7" s="4">
-        <v>0.7909999999999999</v>
+        <v>0.7829999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2042,10 +2042,10 @@
         <v>89</v>
       </c>
       <c r="C8">
-        <v>1099</v>
+        <v>1035</v>
       </c>
       <c r="D8" s="4">
-        <v>0.8059999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2056,10 +2056,10 @@
         <v>86</v>
       </c>
       <c r="C9">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="D9" s="4">
-        <v>0.672</v>
+        <v>0.6709999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2070,10 +2070,10 @@
         <v>87</v>
       </c>
       <c r="C10">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="D10" s="4">
-        <v>0.741</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2084,10 +2084,10 @@
         <v>88</v>
       </c>
       <c r="C11">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="D11" s="4">
-        <v>0.779</v>
+        <v>0.777</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2098,10 +2098,10 @@
         <v>89</v>
       </c>
       <c r="C12">
-        <v>835</v>
+        <v>804</v>
       </c>
       <c r="D12" s="4">
-        <v>0.78</v>
+        <v>0.777</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2112,10 +2112,10 @@
         <v>86</v>
       </c>
       <c r="C13">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="D13" s="4">
-        <v>0.6679999999999999</v>
+        <v>0.6829999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2126,10 +2126,10 @@
         <v>87</v>
       </c>
       <c r="C14">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D14" s="4">
-        <v>0.737</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2140,10 +2140,10 @@
         <v>88</v>
       </c>
       <c r="C15">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="D15" s="4">
-        <v>0.7290000000000001</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2154,10 +2154,10 @@
         <v>89</v>
       </c>
       <c r="C16">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="D16" s="4">
-        <v>0.8149999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2168,10 +2168,10 @@
         <v>86</v>
       </c>
       <c r="C17">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="D17" s="4">
-        <v>0.727</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2182,10 +2182,10 @@
         <v>87</v>
       </c>
       <c r="C18">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D18" s="4">
-        <v>0.765</v>
+        <v>0.7759999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2196,10 +2196,10 @@
         <v>88</v>
       </c>
       <c r="C19">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="D19" s="4">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2210,10 +2210,10 @@
         <v>89</v>
       </c>
       <c r="C20">
-        <v>538</v>
+        <v>579</v>
       </c>
       <c r="D20" s="4">
-        <v>0.8070000000000001</v>
+        <v>0.7959999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2224,10 +2224,10 @@
         <v>86</v>
       </c>
       <c r="C21">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="D21" s="4">
-        <v>0.696</v>
+        <v>0.698</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2238,10 +2238,10 @@
         <v>87</v>
       </c>
       <c r="C22">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="D22" s="4">
-        <v>0.74</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2252,10 +2252,10 @@
         <v>88</v>
       </c>
       <c r="C23">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D23" s="4">
-        <v>0.752</v>
+        <v>0.758</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2266,10 +2266,10 @@
         <v>89</v>
       </c>
       <c r="C24">
-        <v>691</v>
+        <v>707</v>
       </c>
       <c r="D24" s="4">
-        <v>0.799</v>
+        <v>0.8029999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">

--- a/task193/golden/sequence_screen_2027Q1.xlsx
+++ b/task193/golden/sequence_screen_2027Q1.xlsx
@@ -1550,10 +1550,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>6801</v>
+        <v>5253</v>
       </c>
       <c r="D5">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="E5" s="5">
         <v>4</v>
@@ -1567,10 +1567,10 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>6182</v>
+        <v>4801</v>
       </c>
       <c r="D6">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="E6" s="5">
         <v>5</v>
@@ -1584,10 +1584,10 @@
         <v>55</v>
       </c>
       <c r="C7">
-        <v>6303</v>
+        <v>4848</v>
       </c>
       <c r="D7">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E7" s="5">
         <v>4</v>
@@ -1601,10 +1601,10 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>6380</v>
+        <v>4329</v>
       </c>
       <c r="D8">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E8" s="5">
         <v>6</v>
@@ -1618,10 +1618,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>3758</v>
+        <v>3364</v>
       </c>
       <c r="D9">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E9" s="5">
         <v>3</v>
@@ -1635,10 +1635,10 @@
         <v>54</v>
       </c>
       <c r="C10">
-        <v>3268</v>
+        <v>2949</v>
       </c>
       <c r="D10">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E10" s="5">
         <v>4</v>
@@ -1652,10 +1652,10 @@
         <v>55</v>
       </c>
       <c r="C11">
-        <v>3233</v>
+        <v>2940</v>
       </c>
       <c r="D11">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E11" s="5">
         <v>4</v>
@@ -1669,13 +1669,13 @@
         <v>56</v>
       </c>
       <c r="C12">
-        <v>3477</v>
+        <v>2923</v>
       </c>
       <c r="D12">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E12" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1686,10 +1686,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>3474</v>
+        <v>4687</v>
       </c>
       <c r="D13">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="E13" s="5">
         <v>4</v>
@@ -1703,10 +1703,10 @@
         <v>54</v>
       </c>
       <c r="C14">
-        <v>3187</v>
+        <v>4281</v>
       </c>
       <c r="D14">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E14" s="5">
         <v>4</v>
@@ -1720,13 +1720,13 @@
         <v>55</v>
       </c>
       <c r="C15">
-        <v>2982</v>
+        <v>4101</v>
       </c>
       <c r="D15">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="E15" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1737,10 +1737,10 @@
         <v>56</v>
       </c>
       <c r="C16">
-        <v>3376</v>
+        <v>5325</v>
       </c>
       <c r="D16">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="E16" s="5">
         <v>5</v>
@@ -1754,13 +1754,13 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>2272</v>
+        <v>2995</v>
       </c>
       <c r="D17">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E17" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1771,13 +1771,13 @@
         <v>54</v>
       </c>
       <c r="C18">
-        <v>2035</v>
+        <v>2620</v>
       </c>
       <c r="D18">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E18" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1788,10 +1788,10 @@
         <v>55</v>
       </c>
       <c r="C19">
-        <v>1928</v>
+        <v>2536</v>
       </c>
       <c r="D19">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E19" s="5">
         <v>7</v>
@@ -1805,13 +1805,13 @@
         <v>56</v>
       </c>
       <c r="C20">
-        <v>2039</v>
+        <v>2677</v>
       </c>
       <c r="D20">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E20" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1862,10 +1862,10 @@
         <v>67</v>
       </c>
       <c r="C5" s="10">
-        <v>265803</v>
+        <v>265024</v>
       </c>
       <c r="D5" s="11">
-        <v>343410</v>
+        <v>342367</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1876,10 +1876,10 @@
         <v>69</v>
       </c>
       <c r="C6" s="10">
-        <v>402972</v>
+        <v>402906</v>
       </c>
       <c r="D6" s="11">
-        <v>530069</v>
+        <v>529981</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1890,10 +1890,10 @@
         <v>71</v>
       </c>
       <c r="C7" s="10">
-        <v>407628</v>
+        <v>407428</v>
       </c>
       <c r="D7" s="11">
-        <v>544717</v>
+        <v>544449</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1904,10 +1904,10 @@
         <v>73</v>
       </c>
       <c r="C8" s="10">
-        <v>383670</v>
+        <v>383410</v>
       </c>
       <c r="D8" s="11">
-        <v>477132</v>
+        <v>476809</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1918,10 +1918,10 @@
         <v>75</v>
       </c>
       <c r="C9" s="10">
-        <v>595422</v>
+        <v>594748</v>
       </c>
       <c r="D9" s="11">
-        <v>747180</v>
+        <v>746325</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1932,10 +1932,10 @@
         <v>77</v>
       </c>
       <c r="C10" s="10">
-        <v>1027964</v>
+        <v>1023684</v>
       </c>
       <c r="D10" s="11">
-        <v>1068764</v>
+        <v>1064159</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1946,10 +1946,10 @@
         <v>79</v>
       </c>
       <c r="C11" s="10">
-        <v>227367</v>
+        <v>227031</v>
       </c>
       <c r="D11" s="11">
-        <v>333093</v>
+        <v>332600</v>
       </c>
     </row>
   </sheetData>
@@ -2014,10 +2014,10 @@
         <v>87</v>
       </c>
       <c r="C6">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D6" s="4">
-        <v>0.695</v>
+        <v>0.6940000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2056,10 +2056,10 @@
         <v>86</v>
       </c>
       <c r="C9">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D9" s="4">
-        <v>0.6709999999999999</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2070,10 +2070,10 @@
         <v>87</v>
       </c>
       <c r="C10">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D10" s="4">
-        <v>0.736</v>
+        <v>0.7340000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2084,10 +2084,10 @@
         <v>88</v>
       </c>
       <c r="C11">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D11" s="4">
-        <v>0.777</v>
+        <v>0.7759999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2098,7 +2098,7 @@
         <v>89</v>
       </c>
       <c r="C12">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D12" s="4">
         <v>0.777</v>
@@ -2126,10 +2126,10 @@
         <v>87</v>
       </c>
       <c r="C14">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D14" s="4">
-        <v>0.715</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2140,10 +2140,10 @@
         <v>88</v>
       </c>
       <c r="C15">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D15" s="4">
-        <v>0.752</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2154,10 +2154,10 @@
         <v>89</v>
       </c>
       <c r="C16">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D16" s="4">
-        <v>0.8100000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2168,10 +2168,10 @@
         <v>86</v>
       </c>
       <c r="C17">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="D17" s="4">
-        <v>0.722</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2196,10 +2196,10 @@
         <v>88</v>
       </c>
       <c r="C19">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D19" s="4">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2210,10 +2210,10 @@
         <v>89</v>
       </c>
       <c r="C20">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="D20" s="4">
-        <v>0.7959999999999999</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2224,10 +2224,10 @@
         <v>86</v>
       </c>
       <c r="C21">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D21" s="4">
-        <v>0.698</v>
+        <v>0.6990000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2238,10 +2238,10 @@
         <v>87</v>
       </c>
       <c r="C22">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D22" s="4">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2252,10 +2252,10 @@
         <v>88</v>
       </c>
       <c r="C23">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D23" s="4">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2266,10 +2266,10 @@
         <v>89</v>
       </c>
       <c r="C24">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D24" s="4">
-        <v>0.8029999999999999</v>
+        <v>0.804</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2280,10 +2280,10 @@
         <v>86</v>
       </c>
       <c r="C25">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D25" s="4">
-        <v>0.705</v>
+        <v>0.7040000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2294,10 +2294,10 @@
         <v>87</v>
       </c>
       <c r="C26">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D26" s="4">
-        <v>0.875</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2308,10 +2308,10 @@
         <v>88</v>
       </c>
       <c r="C27">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D27" s="4">
-        <v>0.725</v>
+        <v>0.7609999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2322,10 +2322,10 @@
         <v>89</v>
       </c>
       <c r="C28">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D28" s="4">
-        <v>0.787</v>
+        <v>0.773</v>
       </c>
     </row>
   </sheetData>

--- a/task193/golden/sequence_screen_2027Q1.xlsx
+++ b/task193/golden/sequence_screen_2027Q1.xlsx
@@ -1433,10 +1433,10 @@
         <v>29</v>
       </c>
       <c r="D27">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E27">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F27">
         <v>135</v>
@@ -1445,7 +1445,7 @@
         <v>0.7859999999999999</v>
       </c>
       <c r="H27" s="5">
-        <v>331.4</v>
+        <v>330.9</v>
       </c>
       <c r="I27" s="6">
         <v>1.5</v>
@@ -1550,10 +1550,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>5253</v>
+        <v>6265</v>
       </c>
       <c r="D5">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="E5" s="5">
         <v>4</v>
@@ -1567,10 +1567,10 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>4801</v>
+        <v>5675</v>
       </c>
       <c r="D6">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E6" s="5">
         <v>5</v>
@@ -1584,10 +1584,10 @@
         <v>55</v>
       </c>
       <c r="C7">
-        <v>4848</v>
+        <v>5731</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E7" s="5">
         <v>4</v>
@@ -1601,10 +1601,10 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>4329</v>
+        <v>5665</v>
       </c>
       <c r="D8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E8" s="5">
         <v>6</v>
@@ -1618,10 +1618,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>3364</v>
+        <v>3330</v>
       </c>
       <c r="D9">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E9" s="5">
         <v>3</v>
@@ -1635,10 +1635,10 @@
         <v>54</v>
       </c>
       <c r="C10">
-        <v>2949</v>
+        <v>2990</v>
       </c>
       <c r="D10">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E10" s="5">
         <v>4</v>
@@ -1652,10 +1652,10 @@
         <v>55</v>
       </c>
       <c r="C11">
-        <v>2940</v>
+        <v>2975</v>
       </c>
       <c r="D11">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E11" s="5">
         <v>4</v>
@@ -1669,13 +1669,13 @@
         <v>56</v>
       </c>
       <c r="C12">
-        <v>2923</v>
+        <v>2990</v>
       </c>
       <c r="D12">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E12" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1686,10 +1686,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4687</v>
+        <v>3604</v>
       </c>
       <c r="D13">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="E13" s="5">
         <v>4</v>
@@ -1703,10 +1703,10 @@
         <v>54</v>
       </c>
       <c r="C14">
-        <v>4281</v>
+        <v>3271</v>
       </c>
       <c r="D14">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="E14" s="5">
         <v>4</v>
@@ -1720,13 +1720,13 @@
         <v>55</v>
       </c>
       <c r="C15">
-        <v>4101</v>
+        <v>3077</v>
       </c>
       <c r="D15">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="E15" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1737,13 +1737,13 @@
         <v>56</v>
       </c>
       <c r="C16">
-        <v>5325</v>
+        <v>3690</v>
       </c>
       <c r="D16">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E16" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1754,10 +1754,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>2995</v>
+        <v>3109</v>
       </c>
       <c r="D17">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E17" s="5">
         <v>6</v>
@@ -1771,10 +1771,10 @@
         <v>54</v>
       </c>
       <c r="C18">
-        <v>2620</v>
+        <v>2729</v>
       </c>
       <c r="D18">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E18" s="5">
         <v>6</v>
@@ -1788,10 +1788,10 @@
         <v>55</v>
       </c>
       <c r="C19">
-        <v>2536</v>
+        <v>2665</v>
       </c>
       <c r="D19">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E19" s="5">
         <v>7</v>
@@ -1805,10 +1805,10 @@
         <v>56</v>
       </c>
       <c r="C20">
-        <v>2677</v>
+        <v>2922</v>
       </c>
       <c r="D20">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E20" s="5">
         <v>6</v>
@@ -1862,10 +1862,10 @@
         <v>67</v>
       </c>
       <c r="C5" s="10">
-        <v>265024</v>
+        <v>265203</v>
       </c>
       <c r="D5" s="11">
-        <v>342367</v>
+        <v>342608</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1876,10 +1876,10 @@
         <v>69</v>
       </c>
       <c r="C6" s="10">
-        <v>402906</v>
+        <v>403788</v>
       </c>
       <c r="D6" s="11">
-        <v>529981</v>
+        <v>531163</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1890,10 +1890,10 @@
         <v>71</v>
       </c>
       <c r="C7" s="10">
-        <v>407428</v>
+        <v>407642</v>
       </c>
       <c r="D7" s="11">
-        <v>544449</v>
+        <v>544736</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1904,10 +1904,10 @@
         <v>73</v>
       </c>
       <c r="C8" s="10">
-        <v>383410</v>
+        <v>383500</v>
       </c>
       <c r="D8" s="11">
-        <v>476809</v>
+        <v>476921</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1918,10 +1918,10 @@
         <v>75</v>
       </c>
       <c r="C9" s="10">
-        <v>594748</v>
+        <v>595146</v>
       </c>
       <c r="D9" s="11">
-        <v>746325</v>
+        <v>746846</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1932,10 +1932,10 @@
         <v>77</v>
       </c>
       <c r="C10" s="10">
-        <v>1023684</v>
+        <v>1027312</v>
       </c>
       <c r="D10" s="11">
-        <v>1064159</v>
+        <v>1068056</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1946,10 +1946,10 @@
         <v>79</v>
       </c>
       <c r="C11" s="10">
-        <v>227031</v>
+        <v>227010</v>
       </c>
       <c r="D11" s="11">
-        <v>332600</v>
+        <v>332570</v>
       </c>
     </row>
   </sheetData>
@@ -2255,7 +2255,7 @@
         <v>585</v>
       </c>
       <c r="D23" s="4">
-        <v>0.757</v>
+        <v>0.7559999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">

--- a/task193/golden/sequence_screen_2027Q1.xlsx
+++ b/task193/golden/sequence_screen_2027Q1.xlsx
@@ -282,16 +282,16 @@
     <t>Hovedstaden</t>
   </si>
   <si>
-    <t>18-34</t>
-  </si>
-  <si>
-    <t>35-44</t>
-  </si>
-  <si>
-    <t>45-64</t>
-  </si>
-  <si>
-    <t>65 and over</t>
+    <t>18-24</t>
+  </si>
+  <si>
+    <t>25-44</t>
+  </si>
+  <si>
+    <t>45-74</t>
+  </si>
+  <si>
+    <t>75 and over</t>
   </si>
   <si>
     <t>Midtjylland</t>
@@ -1865,7 +1865,7 @@
         <v>265203</v>
       </c>
       <c r="D5" s="11">
-        <v>342608</v>
+        <v>333475</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1876,10 +1876,10 @@
         <v>69</v>
       </c>
       <c r="C6" s="10">
-        <v>403788</v>
+        <v>472479</v>
       </c>
       <c r="D6" s="11">
-        <v>531163</v>
+        <v>597898</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1893,7 +1893,7 @@
         <v>407642</v>
       </c>
       <c r="D7" s="11">
-        <v>544736</v>
+        <v>536131</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1904,10 +1904,10 @@
         <v>73</v>
       </c>
       <c r="C8" s="10">
-        <v>383500</v>
+        <v>191750</v>
       </c>
       <c r="D8" s="11">
-        <v>476921</v>
+        <v>288316</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1921,7 +1921,7 @@
         <v>595146</v>
       </c>
       <c r="D9" s="11">
-        <v>746846</v>
+        <v>719749</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1935,7 +1935,7 @@
         <v>1027312</v>
       </c>
       <c r="D10" s="11">
-        <v>1068056</v>
+        <v>1032066</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1946,10 +1946,10 @@
         <v>79</v>
       </c>
       <c r="C11" s="10">
-        <v>227010</v>
+        <v>113505</v>
       </c>
       <c r="D11" s="11">
-        <v>332570</v>
+        <v>170258</v>
       </c>
     </row>
   </sheetData>
@@ -2000,10 +2000,10 @@
         <v>86</v>
       </c>
       <c r="C5">
-        <v>638</v>
+        <v>251</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6909999999999999</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2014,10 +2014,10 @@
         <v>87</v>
       </c>
       <c r="C6">
-        <v>366</v>
+        <v>753</v>
       </c>
       <c r="D6" s="4">
-        <v>0.6940000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2028,10 +2028,10 @@
         <v>88</v>
       </c>
       <c r="C7">
-        <v>734</v>
+        <v>1090</v>
       </c>
       <c r="D7" s="4">
-        <v>0.7829999999999999</v>
+        <v>0.7979999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2042,10 +2042,10 @@
         <v>89</v>
       </c>
       <c r="C8">
-        <v>1035</v>
+        <v>679</v>
       </c>
       <c r="D8" s="4">
-        <v>0.8120000000000001</v>
+        <v>0.8029999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2056,10 +2056,10 @@
         <v>86</v>
       </c>
       <c r="C9">
-        <v>498</v>
+        <v>209</v>
       </c>
       <c r="D9" s="4">
-        <v>0.669</v>
+        <v>0.6890000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2070,10 +2070,10 @@
         <v>87</v>
       </c>
       <c r="C10">
-        <v>308</v>
+        <v>597</v>
       </c>
       <c r="D10" s="4">
-        <v>0.7340000000000001</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2084,10 +2084,10 @@
         <v>88</v>
       </c>
       <c r="C11">
-        <v>590</v>
+        <v>878</v>
       </c>
       <c r="D11" s="4">
-        <v>0.7759999999999999</v>
+        <v>0.7809999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2098,10 +2098,10 @@
         <v>89</v>
       </c>
       <c r="C12">
-        <v>803</v>
+        <v>515</v>
       </c>
       <c r="D12" s="4">
-        <v>0.777</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2112,10 +2112,10 @@
         <v>86</v>
       </c>
       <c r="C13">
-        <v>249</v>
+        <v>91</v>
       </c>
       <c r="D13" s="4">
-        <v>0.6829999999999999</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2126,10 +2126,10 @@
         <v>87</v>
       </c>
       <c r="C14">
-        <v>143</v>
+        <v>301</v>
       </c>
       <c r="D14" s="4">
-        <v>0.72</v>
+        <v>0.6940000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2140,10 +2140,10 @@
         <v>88</v>
       </c>
       <c r="C15">
-        <v>308</v>
+        <v>451</v>
       </c>
       <c r="D15" s="4">
-        <v>0.747</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2154,10 +2154,10 @@
         <v>89</v>
       </c>
       <c r="C16">
-        <v>371</v>
+        <v>228</v>
       </c>
       <c r="D16" s="4">
-        <v>0.8090000000000001</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2168,10 +2168,10 @@
         <v>86</v>
       </c>
       <c r="C17">
-        <v>310</v>
+        <v>130</v>
       </c>
       <c r="D17" s="4">
-        <v>0.723</v>
+        <v>0.6920000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2182,10 +2182,10 @@
         <v>87</v>
       </c>
       <c r="C18">
-        <v>205</v>
+        <v>385</v>
       </c>
       <c r="D18" s="4">
-        <v>0.7759999999999999</v>
+        <v>0.7609999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2196,10 +2196,10 @@
         <v>88</v>
       </c>
       <c r="C19">
-        <v>439</v>
+        <v>653</v>
       </c>
       <c r="D19" s="4">
-        <v>0.754</v>
+        <v>0.7659999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2210,10 +2210,10 @@
         <v>89</v>
       </c>
       <c r="C20">
-        <v>576</v>
+        <v>362</v>
       </c>
       <c r="D20" s="4">
-        <v>0.799</v>
+        <v>0.804</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2224,10 +2224,10 @@
         <v>86</v>
       </c>
       <c r="C21">
-        <v>495</v>
+        <v>197</v>
       </c>
       <c r="D21" s="4">
-        <v>0.6990000000000001</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2238,10 +2238,10 @@
         <v>87</v>
       </c>
       <c r="C22">
-        <v>267</v>
+        <v>565</v>
       </c>
       <c r="D22" s="4">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2252,10 +2252,10 @@
         <v>88</v>
       </c>
       <c r="C23">
-        <v>585</v>
+        <v>866</v>
       </c>
       <c r="D23" s="4">
-        <v>0.7559999999999999</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2266,10 +2266,10 @@
         <v>89</v>
       </c>
       <c r="C24">
-        <v>705</v>
+        <v>424</v>
       </c>
       <c r="D24" s="4">
-        <v>0.804</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2280,10 +2280,10 @@
         <v>86</v>
       </c>
       <c r="C25">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="D25" s="4">
-        <v>0.7040000000000001</v>
+        <v>0.7240000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2294,10 +2294,10 @@
         <v>87</v>
       </c>
       <c r="C26">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="D26" s="4">
-        <v>0.85</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2308,10 +2308,10 @@
         <v>88</v>
       </c>
       <c r="C27">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D27" s="4">
-        <v>0.7609999999999999</v>
+        <v>0.757</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2322,10 +2322,10 @@
         <v>89</v>
       </c>
       <c r="C28">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="D28" s="4">
-        <v>0.773</v>
+        <v>0.7859999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/task193/golden/sequence_screen_2027Q1.xlsx
+++ b/task193/golden/sequence_screen_2027Q1.xlsx
@@ -933,19 +933,19 @@
         <v>23</v>
       </c>
       <c r="D11">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E11">
         <v>91</v>
       </c>
       <c r="F11">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G11" s="4">
-        <v>0.529</v>
+        <v>0.532</v>
       </c>
       <c r="H11" s="5">
-        <v>92.7</v>
+        <v>92.5</v>
       </c>
       <c r="I11" s="6">
         <v>0.98</v>
@@ -1029,22 +1029,22 @@
         <v>23</v>
       </c>
       <c r="D14">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E14">
         <v>63</v>
       </c>
       <c r="F14">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G14" s="4">
-        <v>0.194</v>
+        <v>0.196</v>
       </c>
       <c r="H14" s="5">
-        <v>67.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="I14" s="6">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J14" t="s">
         <v>16</v>
@@ -1125,19 +1125,19 @@
         <v>29</v>
       </c>
       <c r="D17">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E17">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F17">
         <v>359</v>
       </c>
       <c r="G17" s="4">
-        <v>0.285</v>
+        <v>0.283</v>
       </c>
       <c r="H17" s="5">
-        <v>140.7</v>
+        <v>139.7</v>
       </c>
       <c r="I17" s="6">
         <v>1.02</v>
@@ -1157,19 +1157,19 @@
         <v>26</v>
       </c>
       <c r="D18">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E18">
         <v>227</v>
       </c>
       <c r="F18">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G18" s="4">
-        <v>0.8140000000000001</v>
+        <v>0.8170000000000001</v>
       </c>
       <c r="H18" s="5">
-        <v>229.5</v>
+        <v>229.4</v>
       </c>
       <c r="I18" s="6">
         <v>0.99</v>
@@ -1433,19 +1433,19 @@
         <v>29</v>
       </c>
       <c r="D27">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E27">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F27">
         <v>135</v>
       </c>
       <c r="G27" s="4">
-        <v>0.7859999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="H27" s="5">
-        <v>330.9</v>
+        <v>329.6</v>
       </c>
       <c r="I27" s="6">
         <v>1.5</v>
@@ -1550,10 +1550,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>6265</v>
+        <v>6287</v>
       </c>
       <c r="D5">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="E5" s="5">
         <v>4</v>
@@ -1567,10 +1567,10 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>5675</v>
+        <v>5669</v>
       </c>
       <c r="D6">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E6" s="5">
         <v>5</v>
@@ -1584,10 +1584,10 @@
         <v>55</v>
       </c>
       <c r="C7">
-        <v>5731</v>
+        <v>5739</v>
       </c>
       <c r="D7">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E7" s="5">
         <v>4</v>
@@ -1601,10 +1601,10 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>5665</v>
+        <v>5666</v>
       </c>
       <c r="D8">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E8" s="5">
         <v>6</v>
@@ -1618,10 +1618,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>3330</v>
+        <v>3331</v>
       </c>
       <c r="D9">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E9" s="5">
         <v>3</v>
@@ -1635,10 +1635,10 @@
         <v>54</v>
       </c>
       <c r="C10">
-        <v>2990</v>
+        <v>2982</v>
       </c>
       <c r="D10">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E10" s="5">
         <v>4</v>
@@ -1652,10 +1652,10 @@
         <v>55</v>
       </c>
       <c r="C11">
-        <v>2975</v>
+        <v>2965</v>
       </c>
       <c r="D11">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E11" s="5">
         <v>4</v>
@@ -1669,10 +1669,10 @@
         <v>56</v>
       </c>
       <c r="C12">
-        <v>2990</v>
+        <v>3010</v>
       </c>
       <c r="D12">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E12" s="5">
         <v>6</v>
@@ -1686,10 +1686,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>3604</v>
+        <v>3597</v>
       </c>
       <c r="D13">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E13" s="5">
         <v>4</v>
@@ -1703,10 +1703,10 @@
         <v>54</v>
       </c>
       <c r="C14">
-        <v>3271</v>
+        <v>3258</v>
       </c>
       <c r="D14">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E14" s="5">
         <v>4</v>
@@ -1720,10 +1720,10 @@
         <v>55</v>
       </c>
       <c r="C15">
-        <v>3077</v>
+        <v>3083</v>
       </c>
       <c r="D15">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E15" s="5">
         <v>5</v>
@@ -1737,10 +1737,10 @@
         <v>56</v>
       </c>
       <c r="C16">
-        <v>3690</v>
+        <v>3683</v>
       </c>
       <c r="D16">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E16" s="5">
         <v>4</v>
@@ -1754,10 +1754,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>3109</v>
+        <v>3114</v>
       </c>
       <c r="D17">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E17" s="5">
         <v>6</v>
@@ -1771,10 +1771,10 @@
         <v>54</v>
       </c>
       <c r="C18">
-        <v>2729</v>
+        <v>2716</v>
       </c>
       <c r="D18">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E18" s="5">
         <v>6</v>
@@ -1788,10 +1788,10 @@
         <v>55</v>
       </c>
       <c r="C19">
-        <v>2665</v>
+        <v>2673</v>
       </c>
       <c r="D19">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E19" s="5">
         <v>7</v>
@@ -1805,10 +1805,10 @@
         <v>56</v>
       </c>
       <c r="C20">
-        <v>2922</v>
+        <v>2924</v>
       </c>
       <c r="D20">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E20" s="5">
         <v>6</v>
@@ -1862,10 +1862,10 @@
         <v>67</v>
       </c>
       <c r="C5" s="10">
-        <v>265203</v>
+        <v>263773</v>
       </c>
       <c r="D5" s="11">
-        <v>333475</v>
+        <v>330714</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1876,10 +1876,10 @@
         <v>69</v>
       </c>
       <c r="C6" s="10">
-        <v>472479</v>
+        <v>472215</v>
       </c>
       <c r="D6" s="11">
-        <v>597898</v>
+        <v>594024</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1890,10 +1890,10 @@
         <v>71</v>
       </c>
       <c r="C7" s="10">
-        <v>407642</v>
+        <v>407056</v>
       </c>
       <c r="D7" s="11">
-        <v>536131</v>
+        <v>522466</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1904,10 +1904,10 @@
         <v>73</v>
       </c>
       <c r="C8" s="10">
-        <v>191750</v>
+        <v>192160</v>
       </c>
       <c r="D8" s="11">
-        <v>288316</v>
+        <v>285555</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1918,10 +1918,10 @@
         <v>75</v>
       </c>
       <c r="C9" s="10">
-        <v>595146</v>
+        <v>592862</v>
       </c>
       <c r="D9" s="11">
-        <v>719749</v>
+        <v>728677</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1932,10 +1932,10 @@
         <v>77</v>
       </c>
       <c r="C10" s="10">
-        <v>1027312</v>
+        <v>1027258</v>
       </c>
       <c r="D10" s="11">
-        <v>1032066</v>
+        <v>1067099</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1946,10 +1946,10 @@
         <v>79</v>
       </c>
       <c r="C11" s="10">
-        <v>113505</v>
+        <v>114082.5</v>
       </c>
       <c r="D11" s="11">
-        <v>170258</v>
+        <v>168728</v>
       </c>
     </row>
   </sheetData>
@@ -2017,7 +2017,7 @@
         <v>753</v>
       </c>
       <c r="D6" s="4">
-        <v>0.6879999999999999</v>
+        <v>0.6890000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2028,7 +2028,7 @@
         <v>88</v>
       </c>
       <c r="C7">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D7" s="4">
         <v>0.7979999999999999</v>
@@ -2042,7 +2042,7 @@
         <v>89</v>
       </c>
       <c r="C8">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D8" s="4">
         <v>0.8029999999999999</v>
@@ -2070,10 +2070,10 @@
         <v>87</v>
       </c>
       <c r="C10">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D10" s="4">
-        <v>0.695</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2084,10 +2084,10 @@
         <v>88</v>
       </c>
       <c r="C11">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="D11" s="4">
-        <v>0.7809999999999999</v>
+        <v>0.7829999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2098,10 +2098,10 @@
         <v>89</v>
       </c>
       <c r="C12">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D12" s="4">
-        <v>0.769</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2115,7 +2115,7 @@
         <v>91</v>
       </c>
       <c r="D13" s="4">
-        <v>0.703</v>
+        <v>0.6920000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2126,10 +2126,10 @@
         <v>87</v>
       </c>
       <c r="C14">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D14" s="4">
-        <v>0.6940000000000001</v>
+        <v>0.6920000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2140,10 +2140,10 @@
         <v>88</v>
       </c>
       <c r="C15">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D15" s="4">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2154,10 +2154,10 @@
         <v>89</v>
       </c>
       <c r="C16">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D16" s="4">
-        <v>0.794</v>
+        <v>0.7929999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2168,10 +2168,10 @@
         <v>86</v>
       </c>
       <c r="C17">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D17" s="4">
-        <v>0.6920000000000001</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2196,7 +2196,7 @@
         <v>88</v>
       </c>
       <c r="C19">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D19" s="4">
         <v>0.7659999999999999</v>
@@ -2224,10 +2224,10 @@
         <v>86</v>
       </c>
       <c r="C21">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D21" s="4">
-        <v>0.721</v>
+        <v>0.7190000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2238,10 +2238,10 @@
         <v>87</v>
       </c>
       <c r="C22">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D22" s="4">
-        <v>0.72</v>
+        <v>0.7170000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2252,10 +2252,10 @@
         <v>88</v>
       </c>
       <c r="C23">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D23" s="4">
-        <v>0.769</v>
+        <v>0.767</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2266,10 +2266,10 @@
         <v>89</v>
       </c>
       <c r="C24">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D24" s="4">
-        <v>0.8090000000000001</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">

--- a/task193/golden/sequence_screen_2027Q1.xlsx
+++ b/task193/golden/sequence_screen_2027Q1.xlsx
@@ -1550,10 +1550,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>6287</v>
+        <v>6283</v>
       </c>
       <c r="D5">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E5" s="5">
         <v>4</v>
@@ -1567,10 +1567,10 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>5669</v>
+        <v>5657</v>
       </c>
       <c r="D6">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E6" s="5">
         <v>5</v>
@@ -1584,10 +1584,10 @@
         <v>55</v>
       </c>
       <c r="C7">
-        <v>5739</v>
+        <v>5724</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E7" s="5">
         <v>4</v>
@@ -1601,10 +1601,10 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>5666</v>
+        <v>5639</v>
       </c>
       <c r="D8">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E8" s="5">
         <v>6</v>
@@ -1618,10 +1618,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="D9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" s="5">
         <v>3</v>
@@ -1635,10 +1635,10 @@
         <v>54</v>
       </c>
       <c r="C10">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="D10">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E10" s="5">
         <v>4</v>
@@ -1652,10 +1652,10 @@
         <v>55</v>
       </c>
       <c r="C11">
-        <v>2965</v>
+        <v>3025</v>
       </c>
       <c r="D11">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E11" s="5">
         <v>4</v>
@@ -1669,10 +1669,10 @@
         <v>56</v>
       </c>
       <c r="C12">
-        <v>3010</v>
+        <v>3159</v>
       </c>
       <c r="D12">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E12" s="5">
         <v>6</v>
@@ -1720,10 +1720,10 @@
         <v>55</v>
       </c>
       <c r="C15">
-        <v>3083</v>
+        <v>3019</v>
       </c>
       <c r="D15">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E15" s="5">
         <v>5</v>
@@ -1737,10 +1737,10 @@
         <v>56</v>
       </c>
       <c r="C16">
-        <v>3683</v>
+        <v>3473</v>
       </c>
       <c r="D16">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E16" s="5">
         <v>4</v>
@@ -1754,10 +1754,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="D17">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17" s="5">
         <v>6</v>
@@ -1771,10 +1771,10 @@
         <v>54</v>
       </c>
       <c r="C18">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="D18">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E18" s="5">
         <v>6</v>
@@ -1805,10 +1805,10 @@
         <v>56</v>
       </c>
       <c r="C20">
-        <v>2924</v>
+        <v>3005</v>
       </c>
       <c r="D20">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E20" s="5">
         <v>6</v>
@@ -1862,10 +1862,10 @@
         <v>67</v>
       </c>
       <c r="C5" s="10">
-        <v>263773</v>
+        <v>282252</v>
       </c>
       <c r="D5" s="11">
-        <v>330714</v>
+        <v>353865</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1876,10 +1876,10 @@
         <v>69</v>
       </c>
       <c r="C6" s="10">
-        <v>472215</v>
+        <v>503166.5</v>
       </c>
       <c r="D6" s="11">
-        <v>594024</v>
+        <v>632763</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1890,10 +1890,10 @@
         <v>71</v>
       </c>
       <c r="C7" s="10">
-        <v>407056</v>
+        <v>434820</v>
       </c>
       <c r="D7" s="11">
-        <v>522466</v>
+        <v>558081</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1904,10 +1904,10 @@
         <v>73</v>
       </c>
       <c r="C8" s="10">
-        <v>192160</v>
+        <v>204605</v>
       </c>
       <c r="D8" s="11">
-        <v>285555</v>
+        <v>304072</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1918,10 +1918,10 @@
         <v>75</v>
       </c>
       <c r="C9" s="10">
-        <v>592862</v>
+        <v>627178</v>
       </c>
       <c r="D9" s="11">
-        <v>728677</v>
+        <v>770812</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1932,10 +1932,10 @@
         <v>77</v>
       </c>
       <c r="C10" s="10">
-        <v>1027258</v>
+        <v>1090114</v>
       </c>
       <c r="D10" s="11">
-        <v>1067099</v>
+        <v>1132391</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1946,10 +1946,10 @@
         <v>79</v>
       </c>
       <c r="C11" s="10">
-        <v>114082.5</v>
+        <v>121348.5</v>
       </c>
       <c r="D11" s="11">
-        <v>168728</v>
+        <v>179474</v>
       </c>
     </row>
   </sheetData>

--- a/task193/golden/sequence_screen_2027Q1.xlsx
+++ b/task193/golden/sequence_screen_2027Q1.xlsx
@@ -1550,10 +1550,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>6283</v>
+        <v>5265</v>
       </c>
       <c r="D5">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E5" s="5">
         <v>4</v>
@@ -1567,10 +1567,10 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>5657</v>
+        <v>4783</v>
       </c>
       <c r="D6">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E6" s="5">
         <v>5</v>
@@ -1584,10 +1584,10 @@
         <v>55</v>
       </c>
       <c r="C7">
-        <v>5724</v>
+        <v>4877</v>
       </c>
       <c r="D7">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E7" s="5">
         <v>4</v>
@@ -1601,10 +1601,10 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>5639</v>
+        <v>4647</v>
       </c>
       <c r="D8">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E8" s="5">
         <v>6</v>
@@ -1618,10 +1618,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>3330</v>
+        <v>4554</v>
       </c>
       <c r="D9">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="E9" s="5">
         <v>3</v>
@@ -1635,10 +1635,10 @@
         <v>54</v>
       </c>
       <c r="C10">
-        <v>2981</v>
+        <v>4079</v>
       </c>
       <c r="D10">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E10" s="5">
         <v>4</v>
@@ -1652,10 +1652,10 @@
         <v>55</v>
       </c>
       <c r="C11">
-        <v>3025</v>
+        <v>4011</v>
       </c>
       <c r="D11">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E11" s="5">
         <v>4</v>
@@ -1669,10 +1669,10 @@
         <v>56</v>
       </c>
       <c r="C12">
-        <v>3159</v>
+        <v>4380</v>
       </c>
       <c r="D12">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E12" s="5">
         <v>6</v>
@@ -1686,10 +1686,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>3597</v>
+        <v>3777</v>
       </c>
       <c r="D13">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E13" s="5">
         <v>4</v>
@@ -1703,10 +1703,10 @@
         <v>54</v>
       </c>
       <c r="C14">
-        <v>3258</v>
+        <v>3316</v>
       </c>
       <c r="D14">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E14" s="5">
         <v>4</v>
@@ -1720,10 +1720,10 @@
         <v>55</v>
       </c>
       <c r="C15">
-        <v>3019</v>
+        <v>3123</v>
       </c>
       <c r="D15">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E15" s="5">
         <v>5</v>
@@ -1737,10 +1737,10 @@
         <v>56</v>
       </c>
       <c r="C16">
-        <v>3473</v>
+        <v>3613</v>
       </c>
       <c r="D16">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E16" s="5">
         <v>4</v>
@@ -1754,10 +1754,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>3113</v>
+        <v>2719</v>
       </c>
       <c r="D17">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E17" s="5">
         <v>6</v>
@@ -1771,13 +1771,13 @@
         <v>54</v>
       </c>
       <c r="C18">
-        <v>2715</v>
+        <v>2434</v>
       </c>
       <c r="D18">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E18" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1788,10 +1788,10 @@
         <v>55</v>
       </c>
       <c r="C19">
-        <v>2673</v>
+        <v>2419</v>
       </c>
       <c r="D19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E19" s="5">
         <v>7</v>
@@ -1805,10 +1805,10 @@
         <v>56</v>
       </c>
       <c r="C20">
-        <v>3005</v>
+        <v>2633</v>
       </c>
       <c r="D20">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E20" s="5">
         <v>6</v>
@@ -1862,10 +1862,10 @@
         <v>67</v>
       </c>
       <c r="C5" s="10">
-        <v>282252</v>
+        <v>281932</v>
       </c>
       <c r="D5" s="11">
-        <v>353865</v>
+        <v>353483</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1876,10 +1876,10 @@
         <v>69</v>
       </c>
       <c r="C6" s="10">
-        <v>503166.5</v>
+        <v>504333.5</v>
       </c>
       <c r="D6" s="11">
-        <v>632763</v>
+        <v>634199</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1890,10 +1890,10 @@
         <v>71</v>
       </c>
       <c r="C7" s="10">
-        <v>434820</v>
+        <v>434434</v>
       </c>
       <c r="D7" s="11">
-        <v>558081</v>
+        <v>557585</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1904,10 +1904,10 @@
         <v>73</v>
       </c>
       <c r="C8" s="10">
-        <v>204605</v>
+        <v>204690</v>
       </c>
       <c r="D8" s="11">
-        <v>304072</v>
+        <v>304182</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1918,10 +1918,10 @@
         <v>75</v>
       </c>
       <c r="C9" s="10">
-        <v>627178</v>
+        <v>626840</v>
       </c>
       <c r="D9" s="11">
-        <v>770812</v>
+        <v>770394</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1932,10 +1932,10 @@
         <v>77</v>
       </c>
       <c r="C10" s="10">
-        <v>1090114</v>
+        <v>1088808</v>
       </c>
       <c r="D10" s="11">
-        <v>1132391</v>
+        <v>1131025</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1946,10 +1946,10 @@
         <v>79</v>
       </c>
       <c r="C11" s="10">
-        <v>121348.5</v>
+        <v>120991.5</v>
       </c>
       <c r="D11" s="11">
-        <v>179474</v>
+        <v>178946</v>
       </c>
     </row>
   </sheetData>
@@ -2000,10 +2000,10 @@
         <v>86</v>
       </c>
       <c r="C5">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D5" s="4">
-        <v>0.705</v>
+        <v>0.7040000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2014,10 +2014,10 @@
         <v>87</v>
       </c>
       <c r="C6">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D6" s="4">
-        <v>0.6890000000000001</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2028,10 +2028,10 @@
         <v>88</v>
       </c>
       <c r="C7">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="D7" s="4">
-        <v>0.7979999999999999</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2042,10 +2042,10 @@
         <v>89</v>
       </c>
       <c r="C8">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D8" s="4">
-        <v>0.8029999999999999</v>
+        <v>0.804</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2056,10 +2056,10 @@
         <v>86</v>
       </c>
       <c r="C9">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D9" s="4">
-        <v>0.6890000000000001</v>
+        <v>0.6859999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2070,10 +2070,10 @@
         <v>87</v>
       </c>
       <c r="C10">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D10" s="4">
-        <v>0.696</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2084,10 +2084,10 @@
         <v>88</v>
       </c>
       <c r="C11">
-        <v>876</v>
+        <v>864</v>
       </c>
       <c r="D11" s="4">
-        <v>0.7829999999999999</v>
+        <v>0.7809999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2098,10 +2098,10 @@
         <v>89</v>
       </c>
       <c r="C12">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D12" s="4">
-        <v>0.772</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2112,10 +2112,10 @@
         <v>86</v>
       </c>
       <c r="C13">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D13" s="4">
-        <v>0.6920000000000001</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2126,10 +2126,10 @@
         <v>87</v>
       </c>
       <c r="C14">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D14" s="4">
-        <v>0.6920000000000001</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2140,10 +2140,10 @@
         <v>88</v>
       </c>
       <c r="C15">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D15" s="4">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2168,10 +2168,10 @@
         <v>86</v>
       </c>
       <c r="C17">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D17" s="4">
-        <v>0.695</v>
+        <v>0.6970000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2182,10 +2182,10 @@
         <v>87</v>
       </c>
       <c r="C18">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D18" s="4">
-        <v>0.7609999999999999</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2196,10 +2196,10 @@
         <v>88</v>
       </c>
       <c r="C19">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D19" s="4">
-        <v>0.7659999999999999</v>
+        <v>0.767</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2213,7 +2213,7 @@
         <v>362</v>
       </c>
       <c r="D20" s="4">
-        <v>0.804</v>
+        <v>0.7979999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2224,10 +2224,10 @@
         <v>86</v>
       </c>
       <c r="C21">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D21" s="4">
-        <v>0.7190000000000001</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2241,7 +2241,7 @@
         <v>562</v>
       </c>
       <c r="D22" s="4">
-        <v>0.7170000000000001</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2252,10 +2252,10 @@
         <v>88</v>
       </c>
       <c r="C23">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="D23" s="4">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2266,10 +2266,10 @@
         <v>89</v>
       </c>
       <c r="C24">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D24" s="4">
-        <v>0.805</v>
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">

--- a/task193/golden/sequence_screen_2027Q1.xlsx
+++ b/task193/golden/sequence_screen_2027Q1.xlsx
@@ -1865,7 +1865,7 @@
         <v>281932</v>
       </c>
       <c r="D5" s="11">
-        <v>353483</v>
+        <v>355787</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1879,7 +1879,7 @@
         <v>504333.5</v>
       </c>
       <c r="D6" s="11">
-        <v>634199</v>
+        <v>640752</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1893,7 +1893,7 @@
         <v>434434</v>
       </c>
       <c r="D7" s="11">
-        <v>557585</v>
+        <v>577881</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1907,7 +1907,7 @@
         <v>204690</v>
       </c>
       <c r="D8" s="11">
-        <v>304182</v>
+        <v>314750</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1921,7 +1921,7 @@
         <v>626840</v>
       </c>
       <c r="D9" s="11">
-        <v>770394</v>
+        <v>755350</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1935,7 +1935,7 @@
         <v>1088808</v>
       </c>
       <c r="D10" s="11">
-        <v>1131025</v>
+        <v>1139857</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1949,7 +1949,7 @@
         <v>120991.5</v>
       </c>
       <c r="D11" s="11">
-        <v>178946</v>
+        <v>185601</v>
       </c>
     </row>
   </sheetData>

--- a/task193/golden/sequence_screen_2027Q1.xlsx
+++ b/task193/golden/sequence_screen_2027Q1.xlsx
@@ -288,10 +288,10 @@
     <t>25-44</t>
   </si>
   <si>
-    <t>45-74</t>
-  </si>
-  <si>
-    <t>75 and over</t>
+    <t>45-54</t>
+  </si>
+  <si>
+    <t>55 and over</t>
   </si>
   <si>
     <t>Midtjylland</t>
@@ -2028,10 +2028,10 @@
         <v>88</v>
       </c>
       <c r="C7">
-        <v>1085</v>
+        <v>387</v>
       </c>
       <c r="D7" s="4">
-        <v>0.797</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2042,10 +2042,10 @@
         <v>89</v>
       </c>
       <c r="C8">
-        <v>679</v>
+        <v>1377</v>
       </c>
       <c r="D8" s="4">
-        <v>0.804</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2084,10 +2084,10 @@
         <v>88</v>
       </c>
       <c r="C11">
-        <v>864</v>
+        <v>269</v>
       </c>
       <c r="D11" s="4">
-        <v>0.7809999999999999</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2098,10 +2098,10 @@
         <v>89</v>
       </c>
       <c r="C12">
-        <v>511</v>
+        <v>1106</v>
       </c>
       <c r="D12" s="4">
-        <v>0.773</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2140,10 +2140,10 @@
         <v>88</v>
       </c>
       <c r="C15">
-        <v>451</v>
+        <v>171</v>
       </c>
       <c r="D15" s="4">
-        <v>0.774</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2154,10 +2154,10 @@
         <v>89</v>
       </c>
       <c r="C16">
-        <v>227</v>
+        <v>507</v>
       </c>
       <c r="D16" s="4">
-        <v>0.7929999999999999</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2196,10 +2196,10 @@
         <v>88</v>
       </c>
       <c r="C19">
-        <v>657</v>
+        <v>223</v>
       </c>
       <c r="D19" s="4">
-        <v>0.767</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2210,10 +2210,10 @@
         <v>89</v>
       </c>
       <c r="C20">
-        <v>362</v>
+        <v>796</v>
       </c>
       <c r="D20" s="4">
-        <v>0.7979999999999999</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2252,10 +2252,10 @@
         <v>88</v>
       </c>
       <c r="C23">
-        <v>879</v>
+        <v>303</v>
       </c>
       <c r="D23" s="4">
-        <v>0.769</v>
+        <v>0.7290000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2266,10 +2266,10 @@
         <v>89</v>
       </c>
       <c r="C24">
-        <v>429</v>
+        <v>1005</v>
       </c>
       <c r="D24" s="4">
-        <v>0.8070000000000001</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2308,10 +2308,10 @@
         <v>88</v>
       </c>
       <c r="C27">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="D27" s="4">
-        <v>0.757</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2322,10 +2322,10 @@
         <v>89</v>
       </c>
       <c r="C28">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="D28" s="4">
-        <v>0.7859999999999999</v>
+        <v>0.779</v>
       </c>
     </row>
   </sheetData>
